--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,130 +469,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>xcp_gn</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>엑스케이프 강남점</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>xcr_kd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
-        <is>
-          <t>비밀의 화원 동성로점</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>sg_gj</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>비밀의 화원 광주점</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>sg_hd</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>비밀의 숲 홍대점</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>sg_hh</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sg_hj</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>sg_jj</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>비밀의 화원 전주점</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>sg_kd</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>비밀의 화원 건대점</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sg_sm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>비밀의 화원 서면점</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>xcp_gn</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>엑스케이프 강남점</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>xcr_kd</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
         <is>
           <t>엑스크라임 건대점</t>
         </is>
@@ -640,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C281"/>
+  <dimension ref="A1:C304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,12 +795,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pm_hs</t>
+          <t>pa_hd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>파노라마 홍대삼거리점</t>
+          <t>플레이아레나 홍대점</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -918,12 +810,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>qc_mk</t>
+          <t>pm_hs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>퀘스천마크</t>
+          <t>파노라마 홍대삼거리점</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -933,12 +825,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rle_sl2</t>
+          <t>qc_mk</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림2호점</t>
+          <t>퀘스천마크</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -948,12 +840,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rle_sl3</t>
+          <t>rle_sl2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림3호점</t>
+          <t>룸엘이스케이프 신림2호점</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -963,12 +855,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>rle_sl3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>룸엘이스케이프 신림3호점</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -978,12 +870,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -993,12 +885,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1008,27 +900,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>33_kd</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PLAY33 건대점</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>33_kd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>PLAY33 건대점</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1038,12 +930,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1053,12 +945,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1068,12 +960,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1083,12 +975,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1098,12 +990,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1113,12 +1005,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1128,12 +1020,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1143,12 +1035,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1158,12 +1050,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1173,12 +1065,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1188,12 +1080,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1203,12 +1095,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1218,12 +1110,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1233,12 +1125,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1248,12 +1140,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1263,12 +1155,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1278,12 +1170,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1293,12 +1185,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1308,12 +1200,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1323,12 +1215,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1338,12 +1230,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1353,12 +1245,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1368,12 +1260,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1383,12 +1275,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1398,12 +1290,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1413,12 +1305,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1428,12 +1320,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1443,12 +1335,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1458,12 +1350,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1473,12 +1365,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1488,12 +1380,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1503,12 +1395,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1518,27 +1410,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bp_ds</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>비트포비아 던전스텔라</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bp_sd</t>
+          <t>bp_ds</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전</t>
+          <t>비트포비아 던전스텔라</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1548,12 +1440,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cd_ht</t>
+          <t>bp_sd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>코드헌터 강남점</t>
+          <t>비트포비아 서면던전</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1563,12 +1455,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cde_grs</t>
+          <t>cd_ht</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>코드이스케이프 가로수길점</t>
+          <t>코드헌터 강남점</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1578,12 +1470,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>clv_tw</t>
+          <t>cde_grs</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>클레버타운</t>
+          <t>코드이스케이프 가로수길점</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1593,12 +1485,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>de_bp</t>
+          <t>clv_tw</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>도어이스케이프 부평점</t>
+          <t>클레버타운</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1608,12 +1500,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>de_sr</t>
+          <t>d_coder</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 레드점</t>
+          <t>Decoder</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1623,12 +1515,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>de_bp</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>도어이스케이프 부평점</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1638,12 +1530,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>de_sr</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>도어이스케이프 신논현 레드점</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1653,12 +1545,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1668,12 +1560,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>key_el</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>키이스케이프X에버랜드 메모리카니발</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1683,12 +1575,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>key_gn</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>키이스케이프 강남점</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1698,12 +1590,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>key_hd</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>키이스케이프 홍대점</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1713,12 +1605,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>key_el</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>키이스케이프X에버랜드 메모리카니발</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1728,12 +1620,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_gn</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프 강남점</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1743,12 +1635,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>key_hd</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>키이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1758,12 +1650,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1773,12 +1665,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1788,12 +1680,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1803,12 +1695,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1818,12 +1710,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1833,12 +1725,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1848,12 +1740,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1863,12 +1755,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1878,12 +1770,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1893,12 +1785,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1908,12 +1800,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1923,12 +1815,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1938,12 +1830,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1953,12 +1845,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1968,12 +1860,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1983,12 +1875,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1998,12 +1890,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -2013,72 +1905,72 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2088,12 +1980,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2103,12 +1995,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2118,12 +2010,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2133,12 +2025,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2148,12 +2040,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2163,12 +2055,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2178,12 +2070,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2193,12 +2085,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2208,12 +2100,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2223,12 +2115,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2238,12 +2130,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2253,12 +2145,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2268,12 +2160,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2283,12 +2175,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2298,12 +2190,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2313,12 +2205,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2328,12 +2220,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2343,12 +2235,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2358,12 +2250,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2373,12 +2265,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2388,12 +2280,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2403,12 +2295,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2418,12 +2310,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2433,12 +2325,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2448,12 +2340,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>머더파커 전주2호점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2463,12 +2355,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2478,12 +2370,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2493,12 +2385,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2508,12 +2400,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2523,12 +2415,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2538,12 +2430,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2553,12 +2445,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2568,12 +2460,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2583,12 +2475,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2598,12 +2490,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2613,12 +2505,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2628,12 +2520,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2643,12 +2535,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2658,12 +2550,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2673,12 +2565,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2688,12 +2580,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2703,12 +2595,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2718,12 +2610,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2733,12 +2625,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2748,12 +2640,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2763,12 +2655,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2778,12 +2670,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2793,12 +2685,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2808,12 +2700,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2823,12 +2715,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2838,12 +2730,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2853,12 +2745,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sm_hd</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>상상의 문 홍대점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2868,12 +2760,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2883,12 +2775,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2898,12 +2790,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2913,12 +2805,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2928,12 +2820,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2943,12 +2835,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2958,12 +2850,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2973,12 +2865,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>sm_hd</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>상상의 문 홍대점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2988,132 +2880,132 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>bp_dhr</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>비트포비아 대학로점</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>cn_gr</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>코난 방탈출</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3123,12 +3015,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>bp_dhr</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>비트포비아 대학로점</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3138,12 +3030,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3153,12 +3045,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3168,12 +3060,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3183,12 +3075,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>cn_gr</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>코난 방탈출</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3198,12 +3090,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3213,12 +3105,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3228,12 +3120,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3243,12 +3135,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3258,12 +3150,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3273,12 +3165,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3288,12 +3180,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3303,12 +3195,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>mp_kd2</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>머더파커 건대2호점</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3318,12 +3210,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3333,12 +3225,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3348,12 +3240,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3363,12 +3255,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3378,12 +3270,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3393,12 +3285,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3408,12 +3300,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3423,12 +3315,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3438,12 +3330,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3453,12 +3345,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3468,12 +3360,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>머더파커 전주3호점</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3483,12 +3375,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>mp_kd2</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>머더파커 건대2호점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3498,12 +3390,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3513,12 +3405,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3528,12 +3420,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3543,12 +3435,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3558,12 +3450,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3573,12 +3465,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3588,12 +3480,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3603,12 +3495,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3618,12 +3510,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3633,12 +3525,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3648,12 +3540,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3663,12 +3555,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3678,12 +3570,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3693,12 +3585,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3708,12 +3600,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3723,12 +3615,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3738,12 +3630,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3753,12 +3645,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3768,12 +3660,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sg_hd</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3783,12 +3675,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3798,12 +3690,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3813,12 +3705,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3828,12 +3720,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3843,12 +3735,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3858,12 +3750,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3873,12 +3765,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>tcd_sl</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>더 코드 신림점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3888,12 +3780,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3903,12 +3795,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3918,237 +3810,237 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>셜록홈즈 군산수송점</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C229" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>tcd_sl</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>더 코드 신림점</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C233" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4158,12 +4050,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4173,12 +4065,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4188,12 +4080,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4203,12 +4095,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4218,12 +4110,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4233,12 +4125,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4248,12 +4140,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4263,12 +4155,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4278,12 +4170,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4293,12 +4185,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4308,12 +4200,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4323,12 +4215,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4338,12 +4230,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4353,12 +4245,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4368,12 +4260,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4383,12 +4275,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4398,12 +4290,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4413,450 +4305,795 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>dia_mi</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>다이아에그 미스터리인</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C257" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C258" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C259" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C264" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C265" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C266" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C267" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C268" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>dia_mi</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>다이아에그 미스터리인</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
+          <t>sh_bg</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>sh_ig</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>sh_js</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>셜록홈즈 잠실점</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>sh_sd</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>sh_sw</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>셜록홈즈 수원역점 (T.A)</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>sh_ys</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>셜록홈즈 여수점</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>swj_sw</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>소우주</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>tcd_jj</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>더 코드 진주점</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>zw_sh</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>제로월드 서현점</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>cb_hd</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>큐브이스케이프 홍대점</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>cb_jj</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>큐브이스케이프 전주점</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>ee_lc</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>지구별방탈출 라스트시티점</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>er8_gn</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>이룸에이트</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>gk_tk</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>황금열쇠 대구동성로2호점</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>gt_gj</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>시간의 문 광주점</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>sh_db</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>tcd_jgj</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>더 코드 광주</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>ecs_kd</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>이스케이프# 건대점</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>ra_sm</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>룸즈에이 광주상무점</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>zw_gn</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>제로월드 강남점</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>dd_sm</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>덤앤더머 서면점</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>zw_gp</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>제로월드 김포본점</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B304" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C281" t="n">
+      <c r="C304" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C304"/>
+  <dimension ref="A1:C305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,12 +570,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ck_hd</t>
+          <t>bk_hv</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>코드케이 홍대점</t>
+          <t>BLACK H[-]AVEN</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -585,12 +585,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cl_esc</t>
+          <t>ck_hd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>찰리이스케이프</t>
+          <t>코드케이 홍대점</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -600,12 +600,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cl_esc2</t>
+          <t>cl_esc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>찰리이스케이프 2호점</t>
+          <t>찰리이스케이프</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -615,12 +615,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cs_he</t>
+          <t>cl_esc2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>체셔하우스</t>
+          <t>찰리이스케이프 2호점</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -630,12 +630,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dp_tk</t>
+          <t>cs_he</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>딥띵커</t>
+          <t>체셔하우스</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -645,12 +645,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>dp_tk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>딥띵커</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -660,12 +660,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>etp_d</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엔터팟 1호점</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -675,12 +675,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>etp_ui</t>
+          <t>etp_d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엔터팟 2호점</t>
+          <t>엔터팟 1호점</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -690,12 +690,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ft_str1</t>
+          <t>etp_ui</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>판타스트릭 1호점</t>
+          <t>엔터팟 2호점</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -705,12 +705,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ft_str2</t>
+          <t>ft_str1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>판타스트릭 2호점</t>
+          <t>판타스트릭 1호점</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -720,12 +720,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ft_str3</t>
+          <t>ft_str2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>판타스트릭 TGC</t>
+          <t>판타스트릭 2호점</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -735,12 +735,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>my_dam</t>
+          <t>ft_str3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>미스터리담</t>
+          <t>판타스트릭 TGC</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -750,12 +750,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mz_gn</t>
+          <t>my_dam</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>괴담저장소 제일기숙학원</t>
+          <t>미스터리담</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -765,12 +765,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mz_hd</t>
+          <t>mz_gn</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>괴담저장소 한강대 담력훈련</t>
+          <t>괴담저장소 제일기숙학원</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -780,12 +780,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ne_bnr</t>
+          <t>mz_hd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대 보네르관</t>
+          <t>괴담저장소 한강대 담력훈련</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -795,12 +795,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pa_hd</t>
+          <t>ne_bnr</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>플레이아레나 홍대점</t>
+          <t>넥스트에디션 건대 보네르관</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -810,12 +810,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pm_hs</t>
+          <t>pa_hd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>파노라마 홍대삼거리점</t>
+          <t>플레이아레나 홍대점</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -825,12 +825,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>qc_mk</t>
+          <t>pm_hs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>퀘스천마크</t>
+          <t>파노라마 홍대삼거리점</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -840,12 +840,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>rle_sl2</t>
+          <t>qc_mk</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림2호점</t>
+          <t>퀘스천마크</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -855,12 +855,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rle_sl3</t>
+          <t>rle_sl2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림3호점</t>
+          <t>룸엘이스케이프 신림2호점</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -870,12 +870,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>rle_sl3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>룸엘이스케이프 신림3호점</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -885,12 +885,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -900,12 +900,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -915,27 +915,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>33_kd</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PLAY33 건대점</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>33_kd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>PLAY33 건대점</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -945,12 +945,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -960,12 +960,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -975,12 +975,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -990,12 +990,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1005,12 +1005,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1020,12 +1020,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1035,12 +1035,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1050,12 +1050,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1065,12 +1065,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1080,12 +1080,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1095,12 +1095,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1110,12 +1110,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1125,12 +1125,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1140,12 +1140,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1155,12 +1155,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1170,12 +1170,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1185,12 +1185,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1200,12 +1200,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1215,12 +1215,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1230,12 +1230,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1245,12 +1245,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1260,12 +1260,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1275,12 +1275,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1290,12 +1290,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1305,12 +1305,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1320,12 +1320,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1335,12 +1335,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1350,12 +1350,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1365,12 +1365,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1380,12 +1380,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1395,12 +1395,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1410,12 +1410,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1425,27 +1425,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>bp_ds</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>비트포비아 던전스텔라</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bp_sd</t>
+          <t>bp_ds</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전</t>
+          <t>비트포비아 던전스텔라</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1455,12 +1455,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cd_ht</t>
+          <t>bp_sd</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>코드헌터 강남점</t>
+          <t>비트포비아 서면던전</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1470,12 +1470,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cde_grs</t>
+          <t>cd_ht</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>코드이스케이프 가로수길점</t>
+          <t>코드헌터 강남점</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1485,12 +1485,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>clv_tw</t>
+          <t>cde_grs</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>클레버타운</t>
+          <t>코드이스케이프 가로수길점</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1500,12 +1500,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>d_coder</t>
+          <t>clv_tw</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Decoder</t>
+          <t>클레버타운</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1515,12 +1515,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>de_bp</t>
+          <t>d_coder</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>도어이스케이프 부평점</t>
+          <t>Decoder</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1530,12 +1530,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>de_sr</t>
+          <t>de_bp</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 레드점</t>
+          <t>도어이스케이프 부평점</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1545,12 +1545,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>de_sr</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>도어이스케이프 신논현 레드점</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1560,12 +1560,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>epsd_gn</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 강남점</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1575,12 +1575,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1590,12 +1590,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1605,12 +1605,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>key_el</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>키이스케이프X에버랜드 메모리카니발</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1620,12 +1620,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>key_gn</t>
+          <t>key_el</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>키이스케이프 강남점</t>
+          <t>키이스케이프X에버랜드 메모리카니발</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1635,12 +1635,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>key_hd</t>
+          <t>key_gn</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>키이스케이프 홍대점</t>
+          <t>키이스케이프 강남점</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1650,12 +1650,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>key_hd</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>키이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1665,12 +1665,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1680,12 +1680,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1695,12 +1695,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1710,12 +1710,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1725,12 +1725,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1740,12 +1740,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1755,12 +1755,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1770,12 +1770,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1785,12 +1785,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1800,12 +1800,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1815,12 +1815,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1830,12 +1830,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1845,12 +1845,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1860,12 +1860,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1875,12 +1875,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1890,12 +1890,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>sg_jj</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>비밀의 화원 전주점</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1905,12 +1905,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1920,12 +1920,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1935,12 +1935,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1950,12 +1950,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1965,27 +1965,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1995,12 +1995,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2010,12 +2010,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2025,12 +2025,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2040,12 +2040,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ccr_1089</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>쿠쿠룸 1089</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2055,12 +2055,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2070,12 +2070,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2085,12 +2085,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2100,12 +2100,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2115,12 +2115,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2130,12 +2130,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2145,12 +2145,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2160,12 +2160,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2175,12 +2175,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2190,12 +2190,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2205,12 +2205,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2220,12 +2220,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2235,12 +2235,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2250,12 +2250,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2265,12 +2265,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2280,12 +2280,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2295,12 +2295,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2310,12 +2310,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2325,12 +2325,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2340,12 +2340,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2355,12 +2355,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>머더파커 전주2호점</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2370,12 +2370,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2385,12 +2385,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2400,12 +2400,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2415,12 +2415,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2430,12 +2430,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2445,12 +2445,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2460,12 +2460,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2475,12 +2475,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2490,12 +2490,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2505,12 +2505,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2520,12 +2520,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2535,12 +2535,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2550,12 +2550,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2565,12 +2565,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2580,12 +2580,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2595,12 +2595,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2610,12 +2610,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2625,12 +2625,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2640,12 +2640,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2655,12 +2655,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2670,12 +2670,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2685,12 +2685,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2700,12 +2700,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2715,12 +2715,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2730,12 +2730,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2745,12 +2745,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2760,12 +2760,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2775,12 +2775,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2790,12 +2790,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2805,12 +2805,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2820,12 +2820,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2835,12 +2835,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2850,12 +2850,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2865,12 +2865,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>sm_hd</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>상상의 문 홍대점</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2880,12 +2880,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sm_hd</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>상상의 문 홍대점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2895,12 +2895,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2910,12 +2910,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2925,12 +2925,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2940,12 +2940,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2955,12 +2955,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2970,12 +2970,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2985,12 +2985,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3000,27 +3000,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>bp_dhr</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>비트포비아 대학로점</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3030,12 +3030,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>bp_dhr</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>비트포비아 대학로점</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3045,12 +3045,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3060,12 +3060,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3075,12 +3075,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>cn_gr</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>코난 방탈출</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3090,12 +3090,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>cn_gr</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>코난 방탈출</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3105,12 +3105,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3120,12 +3120,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3135,12 +3135,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3150,12 +3150,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3165,12 +3165,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3180,12 +3180,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3195,12 +3195,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3210,12 +3210,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3225,12 +3225,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3240,12 +3240,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3255,12 +3255,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3270,12 +3270,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3285,12 +3285,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3300,12 +3300,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3315,12 +3315,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3330,12 +3330,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3345,12 +3345,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3360,12 +3360,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3375,12 +3375,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>mp_kd2</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>머더파커 건대2호점</t>
+          <t>머더파커 전주3호점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3390,12 +3390,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mp_kd2</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>머더파커 건대2호점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3405,12 +3405,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3420,12 +3420,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3435,12 +3435,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3450,12 +3450,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3465,12 +3465,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3480,12 +3480,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -4680,12 +4680,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4695,12 +4695,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4710,12 +4710,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4725,12 +4725,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4740,12 +4740,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4755,12 +4755,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4770,12 +4770,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4785,12 +4785,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4800,12 +4800,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4815,12 +4815,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4830,12 +4830,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4845,12 +4845,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4860,12 +4860,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4875,27 +4875,27 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4905,12 +4905,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4920,12 +4920,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4935,12 +4935,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4950,12 +4950,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4965,12 +4965,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4980,12 +4980,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4995,27 +4995,27 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5025,12 +5025,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5040,27 +5040,27 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5070,30 +5070,45 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>zw_gp</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>제로월드 김포본점</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C304" t="n">
+      <c r="C305" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -930,12 +930,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>33_kd</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PLAY33 건대점</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -945,12 +945,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -960,12 +960,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -975,12 +975,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -990,12 +990,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1005,12 +1005,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1020,12 +1020,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1035,12 +1035,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1050,12 +1050,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1065,12 +1065,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1080,12 +1080,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1095,12 +1095,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1110,12 +1110,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1125,12 +1125,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1140,12 +1140,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1155,12 +1155,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1170,12 +1170,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1185,12 +1185,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1200,12 +1200,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1215,12 +1215,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1230,12 +1230,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1245,12 +1245,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1260,12 +1260,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1275,12 +1275,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1290,12 +1290,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1305,12 +1305,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1320,12 +1320,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1335,12 +1335,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1350,12 +1350,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1365,12 +1365,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1380,12 +1380,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1395,12 +1395,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1410,12 +1410,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1425,16 +1425,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>33_kd</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>PLAY33 건대점</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -1965,12 +1965,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1980,27 +1980,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2010,12 +2010,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2025,12 +2025,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2040,12 +2040,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2055,12 +2055,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ccr_1089</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>쿠쿠룸 1089</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2070,12 +2070,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2085,12 +2085,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2100,12 +2100,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2115,12 +2115,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2130,12 +2130,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2145,12 +2145,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2160,12 +2160,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2175,12 +2175,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2190,12 +2190,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2205,12 +2205,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2220,12 +2220,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2235,12 +2235,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2250,12 +2250,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2265,12 +2265,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2280,12 +2280,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2295,12 +2295,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2310,12 +2310,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2325,12 +2325,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2340,12 +2340,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2355,12 +2355,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2370,12 +2370,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>머더파커 전주2호점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2385,12 +2385,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2400,12 +2400,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2415,12 +2415,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2430,12 +2430,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2445,12 +2445,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2460,12 +2460,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2475,12 +2475,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2490,12 +2490,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2505,12 +2505,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2520,12 +2520,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2535,12 +2535,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2550,12 +2550,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2565,12 +2565,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2580,12 +2580,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2595,12 +2595,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2610,12 +2610,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2625,12 +2625,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2640,12 +2640,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2655,12 +2655,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2670,12 +2670,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2685,12 +2685,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2700,12 +2700,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2715,12 +2715,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2730,12 +2730,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2745,12 +2745,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2760,12 +2760,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2775,12 +2775,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2790,12 +2790,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2805,12 +2805,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2820,12 +2820,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2835,12 +2835,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2850,12 +2850,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2865,12 +2865,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2880,12 +2880,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>sm_hd</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>상상의 문 홍대점</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2895,12 +2895,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sm_hd</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>상상의 문 홍대점</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2910,12 +2910,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2925,12 +2925,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2940,12 +2940,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2955,12 +2955,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2970,12 +2970,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2985,12 +2985,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C164" t="n">

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C305"/>
+  <dimension ref="A1:C322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -750,12 +750,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>my_dam</t>
+          <t>lt_ss</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>미스터리담</t>
+          <t>레토 성수</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -765,12 +765,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mz_gn</t>
+          <t>my_dam</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>괴담저장소 제일기숙학원</t>
+          <t>미스터리 담</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -780,12 +780,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mz_hd</t>
+          <t>mz_gn</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>괴담저장소 한강대 담력훈련</t>
+          <t>괴담저장소 제일기숙학원</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -795,12 +795,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ne_bnr</t>
+          <t>mz_hd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대 보네르관</t>
+          <t>괴담저장소 한강대 담력훈련</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -810,12 +810,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pa_hd</t>
+          <t>ne_bnr</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>플레이아레나 홍대점</t>
+          <t>넥스트에디션 건대 보네르관</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -825,12 +825,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pm_hs</t>
+          <t>pa_hd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>파노라마 홍대삼거리점</t>
+          <t>플레이아레나 홍대점</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -840,12 +840,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qc_mk</t>
+          <t>pm_bs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>퀘스천마크</t>
+          <t>파노라마 부산점</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -855,12 +855,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>rle_sl2</t>
+          <t>pm_hs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림2호점</t>
+          <t>파노라마 홍대삼거리점</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -870,12 +870,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>rle_sl3</t>
+          <t>pm_lw</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림3호점</t>
+          <t>파노라마X롯데월드</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -885,12 +885,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>qc_mk</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>퀘스천마크</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -900,12 +900,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>rle_sl2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>룸엘이스케이프 신림2호점</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -915,12 +915,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>rle_sl3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>룸엘이스케이프 신림3호점</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -930,57 +930,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -990,12 +990,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1005,12 +1005,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1020,12 +1020,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1035,12 +1035,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1050,12 +1050,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1065,12 +1065,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1080,12 +1080,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1095,12 +1095,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1110,12 +1110,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1125,12 +1125,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1140,12 +1140,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1155,12 +1155,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1170,12 +1170,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1185,12 +1185,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1200,12 +1200,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1215,12 +1215,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1230,12 +1230,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1245,12 +1245,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1260,12 +1260,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1275,12 +1275,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1290,12 +1290,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1305,12 +1305,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1320,12 +1320,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1335,12 +1335,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1350,12 +1350,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1365,12 +1365,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1380,12 +1380,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1395,12 +1395,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1410,12 +1410,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1425,57 +1425,57 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>33_kd</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PLAY33 건대점</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>bp_ds</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>비트포비아 던전스텔라</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>bp_sd</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>cd_ht</t>
+          <t>33_kd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>코드헌터 강남점</t>
+          <t>PLAY33 건대점</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1485,12 +1485,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>cde_grs</t>
+          <t>bp_ds</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>코드이스케이프 가로수길점</t>
+          <t>비트포비아 던전스텔라</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1500,12 +1500,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>clv_tw</t>
+          <t>bp_sd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>클레버타운</t>
+          <t>비트포비아 서면던전</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1515,12 +1515,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>d_coder</t>
+          <t>cd_ht</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Decoder</t>
+          <t>코드헌터 강남점</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1530,12 +1530,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>de_bp</t>
+          <t>cde_grs</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>도어이스케이프 부평점</t>
+          <t>코드이스케이프 가로수길점</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1545,12 +1545,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>de_sr</t>
+          <t>clv_tw</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 레드점</t>
+          <t>클레버타운</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1560,12 +1560,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>d_coder</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>Decoder</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1575,12 +1575,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>epsd_gn</t>
+          <t>de_bp</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 강남점</t>
+          <t>도어이스케이프 부평점</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1590,12 +1590,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>de_sr</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>도어이스케이프 신논현 레드점</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1605,12 +1605,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1620,12 +1620,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>key_el</t>
+          <t>ect_sc</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>키이스케이프X에버랜드 메모리카니발</t>
+          <t>이스케이프시티 그랜드 시티 신촌점</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1635,12 +1635,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>key_gn</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>키이스케이프 강남점</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1650,12 +1650,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>key_hd</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>키이스케이프 홍대점</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1665,12 +1665,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1680,12 +1680,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_el</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프X에버랜드 메모리카니발</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1695,12 +1695,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>key_gn</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>키이스케이프 강남점</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1710,12 +1710,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>key_hd</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>키이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1725,12 +1725,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1740,12 +1740,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1755,12 +1755,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1770,12 +1770,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1785,12 +1785,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1800,12 +1800,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1815,12 +1815,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1830,12 +1830,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1845,12 +1845,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1860,12 +1860,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1875,12 +1875,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>pnc_md</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>패닉이스케이프 목동점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1890,12 +1890,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1905,12 +1905,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>sg_jj</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>비밀의 화원 전주점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1920,12 +1920,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1935,12 +1935,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1950,12 +1950,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1965,12 +1965,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1980,12 +1980,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1995,117 +1995,117 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>sv_kd1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>솔버 1호점</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>sv_kd2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>솔버 2호점</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ccr_1089</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>쿠쿠룸 1089</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2115,12 +2115,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2130,12 +2130,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2145,12 +2145,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2160,12 +2160,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2175,12 +2175,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2190,12 +2190,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2205,12 +2205,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2220,12 +2220,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2235,12 +2235,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2250,12 +2250,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2265,12 +2265,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2280,12 +2280,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2295,12 +2295,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2310,12 +2310,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2325,12 +2325,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2340,12 +2340,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>ect_bc</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>이스케이프시티 부천신중동점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2355,12 +2355,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>ep_lg</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>에필로그</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2370,12 +2370,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2385,12 +2385,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2400,12 +2400,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2415,12 +2415,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2430,12 +2430,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2445,12 +2445,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2460,12 +2460,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2475,12 +2475,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2490,12 +2490,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2505,12 +2505,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>머더파커 전주2호점</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2520,12 +2520,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2535,12 +2535,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2550,12 +2550,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2565,12 +2565,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2580,12 +2580,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2595,12 +2595,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2610,12 +2610,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2625,12 +2625,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2640,12 +2640,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2655,12 +2655,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2670,12 +2670,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2685,12 +2685,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2700,12 +2700,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2715,12 +2715,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2730,12 +2730,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2745,12 +2745,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2760,12 +2760,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2775,12 +2775,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2790,12 +2790,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2805,12 +2805,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2820,12 +2820,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2835,12 +2835,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2850,12 +2850,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2865,12 +2865,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2880,12 +2880,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2895,12 +2895,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>sm_hd</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>상상의 문 홍대점</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2910,12 +2910,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2925,12 +2925,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2940,12 +2940,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2955,12 +2955,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2970,12 +2970,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2985,12 +2985,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3000,12 +3000,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3015,147 +3015,147 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>bp_dhr</t>
+          <t>sm_hd</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>비트포비아 대학로점</t>
+          <t>상상의 문 홍대점</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C169" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>cn_gr</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>코난 방탈출</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3165,12 +3165,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>bp_dhr</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>비트포비아 대학로점</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3180,12 +3180,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3195,12 +3195,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3210,12 +3210,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3225,12 +3225,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>cn_gr</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>코난 방탈출</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3240,12 +3240,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3255,12 +3255,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3270,12 +3270,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3285,12 +3285,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3300,12 +3300,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3315,12 +3315,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3330,12 +3330,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3345,12 +3345,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3360,12 +3360,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3375,12 +3375,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3390,12 +3390,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>mp_kd2</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>머더파커 건대2호점</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3405,12 +3405,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3420,12 +3420,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3435,12 +3435,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3450,12 +3450,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3465,12 +3465,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3480,12 +3480,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3495,12 +3495,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3510,12 +3510,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3525,12 +3525,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3540,12 +3540,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3555,12 +3555,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>머더파커 전주3호점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3570,12 +3570,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>mp_kd2</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>머더파커 건대2호점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3585,12 +3585,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3600,12 +3600,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3615,12 +3615,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3630,12 +3630,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3645,12 +3645,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3660,12 +3660,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>sg_hd</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3675,12 +3675,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3690,12 +3690,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3705,12 +3705,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3720,12 +3720,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3735,12 +3735,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3750,12 +3750,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3765,12 +3765,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3780,12 +3780,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3795,12 +3795,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3810,12 +3810,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3825,12 +3825,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3840,12 +3840,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sg_hd</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3855,12 +3855,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3870,12 +3870,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3885,12 +3885,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3900,12 +3900,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3915,12 +3915,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3930,12 +3930,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3945,12 +3945,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3960,12 +3960,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3975,12 +3975,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3990,12 +3990,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>tcd_sl</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>더 코드 신림점</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4005,12 +4005,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4020,12 +4020,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>셜록홈즈 군산수송점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4035,222 +4035,222 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C234" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C235" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C236" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C237" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C238" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C239" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C240" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C241" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C242" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>tcd_sl</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>더 코드 신림점</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C244" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C245" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4260,12 +4260,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4275,12 +4275,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4290,12 +4290,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4305,12 +4305,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4320,12 +4320,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4335,12 +4335,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4350,12 +4350,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4365,12 +4365,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4380,12 +4380,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4395,12 +4395,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4410,12 +4410,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4425,12 +4425,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4440,12 +4440,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4455,12 +4455,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4470,12 +4470,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4485,12 +4485,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4500,12 +4500,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4515,12 +4515,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4530,12 +4530,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4545,12 +4545,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4560,252 +4560,252 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C269" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C270" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C271" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C272" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>dia_mi</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>다이아에그 미스터리인</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C273" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C274" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C275" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C277" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C278" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C279" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C281" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C282" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C283" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4815,12 +4815,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4830,12 +4830,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4845,12 +4845,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4860,12 +4860,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>dia_mi</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>다이아에그 미스터리인</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4875,12 +4875,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4890,225 +4890,480 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C299" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C300" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C303" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C304" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
+          <t>tcd_jj</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>더 코드 진주점</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>zw_sh</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>제로월드 서현점</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>cb_hd</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>큐브이스케이프 홍대점</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>cb_jj</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>큐브이스케이프 전주점</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>ee_lc</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>지구별방탈출 라스트시티점</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>er8_gn</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>이룸에이트</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>gk_tk</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>황금열쇠 대구동성로2호점</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>gt_gj</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>시간의 문 광주점</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>sh_db</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>tcd_jgj</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>더 코드 광주</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>ecs_kd</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>이스케이프# 건대점</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>ra_sm</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>룸즈에이 광주상무점</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>zw_gn</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>제로월드 강남점</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>mz_nw</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>더메이즈 노원점</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>dd_sm</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>덤앤더머 서면점</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>zw_gp</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>제로월드 김포본점</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C305" t="n">
+      <c r="C322" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C322"/>
+  <dimension ref="A1:C323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,12 +555,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>33_dj</t>
+          <t>bk_hv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PLAY33 대전점</t>
+          <t>BLACK H[-]AVEN</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -570,12 +570,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bk_hv</t>
+          <t>ck_hd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BLACK H[-]AVEN</t>
+          <t>코드케이 홍대점</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -585,12 +585,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ck_hd</t>
+          <t>cl_esc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>코드케이 홍대점</t>
+          <t>찰리이스케이프</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -600,12 +600,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cl_esc</t>
+          <t>cl_esc2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>찰리이스케이프</t>
+          <t>찰리이스케이프 2호점</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -615,12 +615,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cl_esc2</t>
+          <t>cs_he</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>찰리이스케이프 2호점</t>
+          <t>체셔하우스</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -630,12 +630,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cs_he</t>
+          <t>dp_tk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>체셔하우스</t>
+          <t>딥띵커</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -645,12 +645,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dp_tk</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>딥띵커</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -660,12 +660,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>etp_d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>엔터팟 1호점</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -675,12 +675,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>etp_d</t>
+          <t>etp_ui</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엔터팟 1호점</t>
+          <t>엔터팟 2호점</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -690,12 +690,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>etp_ui</t>
+          <t>ft_str1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엔터팟 2호점</t>
+          <t>판타스트릭 1호점</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -705,12 +705,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ft_str1</t>
+          <t>ft_str2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>판타스트릭 1호점</t>
+          <t>판타스트릭 2호점</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -720,12 +720,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ft_str2</t>
+          <t>ft_str3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>판타스트릭 2호점</t>
+          <t>판타스트릭 TGC</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -735,12 +735,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ft_str3</t>
+          <t>lt_ss</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>판타스트릭 TGC</t>
+          <t>레토 성수</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -750,12 +750,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lt_ss</t>
+          <t>my_dam</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>레토 성수</t>
+          <t>미스터리 담</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -765,12 +765,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>my_dam</t>
+          <t>mz_gn</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>미스터리 담</t>
+          <t>괴담저장소 제일기숙학원</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -780,12 +780,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mz_gn</t>
+          <t>mz_hd</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>괴담저장소 제일기숙학원</t>
+          <t>괴담저장소 한강대 담력훈련</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -795,12 +795,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mz_hd</t>
+          <t>ne_bnr</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>괴담저장소 한강대 담력훈련</t>
+          <t>넥스트에디션 건대 보네르관</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -810,12 +810,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ne_bnr</t>
+          <t>pa_hd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대 보네르관</t>
+          <t>플레이아레나 홍대점</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -825,12 +825,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pa_hd</t>
+          <t>pm_bs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>플레이아레나 홍대점</t>
+          <t>파노라마 부산점</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -840,12 +840,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pm_bs</t>
+          <t>pm_hs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>파노라마 부산점</t>
+          <t>파노라마 홍대삼거리점</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -855,12 +855,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pm_hs</t>
+          <t>pm_lw</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>파노라마 홍대삼거리점</t>
+          <t>파노라마X롯데월드</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -870,12 +870,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pm_lw</t>
+          <t>qc_mk</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파노라마X롯데월드</t>
+          <t>퀘스천마크</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -885,12 +885,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>qc_mk</t>
+          <t>rle_sl2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>퀘스천마크</t>
+          <t>룸엘이스케이프 신림2호점</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -900,12 +900,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rle_sl2</t>
+          <t>rle_sl3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림2호점</t>
+          <t>룸엘이스케이프 신림3호점</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -915,12 +915,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rle_sl3</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림3호점</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -930,12 +930,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -945,12 +945,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -960,16 +960,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>33_dj</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -3825,12 +3825,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3840,12 +3840,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>sg_hd</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -4740,12 +4740,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4755,12 +4755,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4770,12 +4770,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4785,12 +4785,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4800,27 +4800,27 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4830,12 +4830,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4845,12 +4845,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4860,12 +4860,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>dia_mi</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>다이아에그 미스터리인</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4875,12 +4875,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>dia_mi</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>다이아에그 미스터리인</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4890,12 +4890,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4905,12 +4905,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4920,12 +4920,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4935,12 +4935,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4950,12 +4950,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4965,12 +4965,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4980,12 +4980,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4995,12 +4995,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -5010,12 +5010,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5025,12 +5025,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5040,12 +5040,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5055,12 +5055,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5070,12 +5070,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5085,12 +5085,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5100,12 +5100,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5115,12 +5115,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5130,27 +5130,27 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5160,12 +5160,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5175,12 +5175,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5190,12 +5190,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5205,12 +5205,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5220,12 +5220,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5235,12 +5235,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5250,27 +5250,27 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5280,12 +5280,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5295,42 +5295,42 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5340,30 +5340,45 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>zw_gp</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>제로월드 김포본점</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C322" t="n">
+      <c r="C323" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -4140,12 +4140,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4155,12 +4155,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>tcd_sl</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>더 코드 신림점</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4170,12 +4170,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>tcd_sl</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>더 코드 신림점</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4185,12 +4185,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4200,12 +4200,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4215,12 +4215,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4230,27 +4230,27 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4260,12 +4260,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4275,12 +4275,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4290,12 +4290,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4305,12 +4305,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4320,12 +4320,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4335,12 +4335,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4350,12 +4350,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4365,12 +4365,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4380,12 +4380,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4395,12 +4395,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4410,12 +4410,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4425,12 +4425,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4440,12 +4440,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4455,12 +4455,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4470,12 +4470,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4485,12 +4485,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4500,12 +4500,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4515,12 +4515,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4530,12 +4530,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4545,12 +4545,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4560,12 +4560,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4575,12 +4575,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4590,12 +4590,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4605,12 +4605,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4620,12 +4620,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4635,12 +4635,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4650,12 +4650,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4665,12 +4665,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4680,12 +4680,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4695,12 +4695,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4710,12 +4710,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4725,12 +4725,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4740,12 +4740,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sh_nbc</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴부천점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4755,12 +4755,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4770,12 +4770,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4785,12 +4785,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C284" t="n">

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,46 +445,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>33_hd</t>
+          <t>nc_kd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PLAY33 홍대점</t>
+          <t>뉴케이스 건대점</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nc_kd</t>
+          <t>xcp_gn</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴케이스 건대점</t>
+          <t>엑스케이프 강남점</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>xcp_gn</t>
+          <t>xcr_kd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
-        <is>
-          <t>엑스케이프 강남점</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>xcr_kd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
         <is>
           <t>엑스크라임 건대점</t>
         </is>
@@ -555,12 +543,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bk_hv</t>
+          <t>33_hd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BLACK H[-]AVEN</t>
+          <t>PLAY33 홍대점</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -570,12 +558,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ck_hd</t>
+          <t>bk_hv</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>코드케이 홍대점</t>
+          <t>BLACK H[-]AVEN</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -585,12 +573,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cl_esc</t>
+          <t>ck_hd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>찰리이스케이프</t>
+          <t>코드케이 홍대점</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -600,12 +588,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cl_esc2</t>
+          <t>cl_esc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>찰리이스케이프 2호점</t>
+          <t>찰리이스케이프</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -615,12 +603,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cs_he</t>
+          <t>cl_esc2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>체셔하우스</t>
+          <t>찰리이스케이프 2호점</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -630,12 +618,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dp_tk</t>
+          <t>cs_he</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>딥띵커</t>
+          <t>체셔하우스</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -645,12 +633,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>dp_tk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>딥띵커</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -660,12 +648,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>etp_d</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엔터팟 1호점</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -675,12 +663,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>etp_ui</t>
+          <t>etp_d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엔터팟 2호점</t>
+          <t>엔터팟 1호점</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -915,12 +903,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>se_ss</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>싸인이스케이프 상수점</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -930,12 +918,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -945,12 +933,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -960,27 +948,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>33_dj</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PLAY33 대전점</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>33_dj</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -990,12 +978,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1005,12 +993,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1020,12 +1008,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1035,12 +1023,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1050,12 +1038,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1065,12 +1053,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1080,12 +1068,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1095,12 +1083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1110,12 +1098,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1125,12 +1113,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1140,12 +1128,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1155,12 +1143,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1170,12 +1158,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1185,12 +1173,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1200,12 +1188,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1215,12 +1203,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1230,12 +1218,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1245,12 +1233,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1260,12 +1248,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1275,12 +1263,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1515,12 +1503,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>cd_ht</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>코드헌터 강남점</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1530,12 +1518,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cde_grs</t>
+          <t>cd_ht</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>코드이스케이프 가로수길점</t>
+          <t>코드헌터 강남점</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1545,12 +1533,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>clv_tw</t>
+          <t>cde_grs</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>클레버타운</t>
+          <t>코드이스케이프 가로수길점</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1560,12 +1548,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>d_coder</t>
+          <t>clv_tw</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Decoder</t>
+          <t>클레버타운</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1575,12 +1563,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>de_bp</t>
+          <t>d_coder</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>도어이스케이프 부평점</t>
+          <t>Decoder</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1590,12 +1578,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>de_sr</t>
+          <t>de_bp</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 레드점</t>
+          <t>도어이스케이프 부평점</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1605,12 +1593,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>de_sr</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>도어이스케이프 신논현 레드점</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1620,12 +1608,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ect_sc</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>이스케이프시티 그랜드 시티 신촌점</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1635,12 +1623,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>epsd_gn</t>
+          <t>ect_sc</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 강남점</t>
+          <t>이스케이프시티 그랜드 시티 신촌점</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1650,12 +1638,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1665,12 +1653,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1680,12 +1668,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>key_el</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>키이스케이프X에버랜드 메모리카니발</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1695,12 +1683,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>key_gn</t>
+          <t>key_el</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>키이스케이프 강남점</t>
+          <t>키이스케이프X에버랜드 메모리카니발</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1710,12 +1698,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>key_hd</t>
+          <t>key_gn</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>키이스케이프 홍대점</t>
+          <t>키이스케이프 강남점</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1725,12 +1713,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>key_hd</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>키이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1740,12 +1728,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1755,12 +1743,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1770,12 +1758,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1785,12 +1773,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1800,12 +1788,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1815,12 +1803,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1830,12 +1818,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1845,12 +1833,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1860,12 +1848,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1875,12 +1863,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>pnc_md</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>패닉이스케이프 목동점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1890,12 +1878,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1905,12 +1893,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>pnc_md</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>패닉이스케이프 목동점</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1920,12 +1908,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1935,12 +1923,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1950,12 +1938,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1965,12 +1953,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1980,12 +1968,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>sg_jj</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>비밀의 화원 전주점</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1995,12 +1983,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2010,12 +1998,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2025,12 +2013,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2040,12 +2028,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>sv_kd1</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>솔버 1호점</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2055,12 +2043,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sv_kd2</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>솔버 2호점</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2070,12 +2058,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>sv_kd1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>솔버 1호점</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2085,12 +2073,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>sv_kd2</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>솔버 2호점</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2100,57 +2088,57 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>sw_lab</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>수원방탈출연구소</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2160,12 +2148,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2175,12 +2163,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ccr_1089</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>쿠쿠룸 1089</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2190,12 +2178,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2205,12 +2193,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2220,12 +2208,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2235,12 +2223,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2250,12 +2238,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2265,12 +2253,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2280,12 +2268,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2295,12 +2283,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2310,12 +2298,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2325,12 +2313,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2340,12 +2328,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ect_bc</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>이스케이프시티 부천신중동점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2355,12 +2343,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ep_lg</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>에필로그</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2370,12 +2358,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>ect_bc</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>이스케이프시티 부천신중동점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2385,12 +2373,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>ep_lg</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>에필로그</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2400,12 +2388,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2415,12 +2403,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2430,12 +2418,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2445,12 +2433,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2460,12 +2448,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2475,12 +2463,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2490,12 +2478,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2505,12 +2493,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2520,12 +2508,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2535,12 +2523,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>머더파커 전주2호점</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2550,12 +2538,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2565,12 +2553,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2580,12 +2568,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2595,12 +2583,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2610,12 +2598,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2625,12 +2613,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2640,12 +2628,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2655,12 +2643,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2670,12 +2658,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2685,12 +2673,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2700,12 +2688,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2715,12 +2703,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2730,12 +2718,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2745,12 +2733,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2760,12 +2748,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2775,12 +2763,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2790,12 +2778,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2805,12 +2793,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2820,12 +2808,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2835,12 +2823,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2850,12 +2838,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2865,12 +2853,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2880,12 +2868,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2895,12 +2883,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2910,12 +2898,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2925,12 +2913,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2940,12 +2928,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2955,12 +2943,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2970,12 +2958,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2985,12 +2973,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3000,12 +2988,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3015,12 +3003,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3030,12 +3018,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>sm_hd</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>상상의 문 홍대점</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3165,12 +3153,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>bp_dhr</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>비트포비아 대학로점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3180,12 +3168,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3195,12 +3183,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3210,12 +3198,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3225,12 +3213,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>cn_gr</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>코난 방탈출</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3240,12 +3228,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>crew_sc2</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>탐정크루 신촌2호점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3255,12 +3243,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3270,12 +3258,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3285,12 +3273,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3300,12 +3288,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3315,12 +3303,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3330,12 +3318,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ect_sswu</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>이스케이프시티 성신여대점</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3345,12 +3333,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3360,12 +3348,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3375,12 +3363,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>find_esc</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>더파인더 방탈출</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3390,12 +3378,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3405,12 +3393,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3420,12 +3408,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3435,12 +3423,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3450,12 +3438,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3465,12 +3453,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3480,12 +3468,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3495,12 +3483,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3510,12 +3498,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3525,12 +3513,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>머더파커 전주3호점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3540,12 +3528,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3555,12 +3543,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3570,12 +3558,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>mp_kd2</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>머더파커 건대2호점</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3585,12 +3573,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3600,12 +3588,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3615,12 +3603,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3630,12 +3618,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3645,12 +3633,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3660,12 +3648,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3675,12 +3663,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3690,12 +3678,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3705,12 +3693,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3720,12 +3708,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3735,12 +3723,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3750,12 +3738,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3765,12 +3753,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3780,12 +3768,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3795,12 +3783,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3810,12 +3798,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3825,12 +3813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3840,12 +3828,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3855,12 +3843,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3870,12 +3858,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3885,12 +3873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3900,12 +3888,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3915,12 +3903,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3930,12 +3918,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3945,12 +3933,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3960,12 +3948,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3975,12 +3963,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3990,12 +3978,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4005,12 +3993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4020,12 +4008,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4035,12 +4023,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4050,12 +4038,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4065,12 +4053,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4080,12 +4068,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4095,12 +4083,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4110,12 +4098,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4125,12 +4113,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4140,12 +4128,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>tcd_sl</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>더 코드 신림점</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4155,12 +4143,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>tcd_sl</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>더 코드 신림점</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4170,12 +4158,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4185,12 +4173,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4200,12 +4188,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4215,27 +4203,27 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4245,12 +4233,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4260,12 +4248,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4275,12 +4263,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4290,12 +4278,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4305,12 +4293,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4320,12 +4308,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4335,12 +4323,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4350,12 +4338,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4365,12 +4353,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4380,12 +4368,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4395,12 +4383,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4410,12 +4398,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4425,12 +4413,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4440,12 +4428,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4455,12 +4443,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4470,12 +4458,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4485,12 +4473,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4500,12 +4488,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4515,12 +4503,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4530,12 +4518,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4545,12 +4533,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4560,12 +4548,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4575,12 +4563,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4590,12 +4578,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4605,12 +4593,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4620,12 +4608,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4635,12 +4623,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4650,12 +4638,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4665,12 +4653,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4680,12 +4668,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4695,12 +4683,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4710,12 +4698,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4725,12 +4713,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>sh_nbc</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴부천점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4740,12 +4728,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4755,12 +4743,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4770,12 +4758,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4785,42 +4773,42 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4830,12 +4818,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4845,12 +4833,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>dia_mi</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>다이아에그 미스터리인</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4860,12 +4848,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4875,12 +4863,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>dia_mi</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>다이아에그 미스터리인</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4890,12 +4878,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4905,12 +4893,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4920,12 +4908,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4935,12 +4923,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4950,12 +4938,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4965,12 +4953,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4980,12 +4968,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4995,12 +4983,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -5010,12 +4998,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5025,12 +5013,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5040,12 +5028,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5055,12 +5043,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5070,12 +5058,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5085,12 +5073,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5100,12 +5088,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5115,42 +5103,42 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5160,12 +5148,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5175,12 +5163,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5190,12 +5178,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5205,12 +5193,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5220,57 +5208,57 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5280,76 +5268,76 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>zw_gp</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>제로월드 김포본점</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>otv_dj</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>오렌지티비 대전은행점</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>otv_dsr</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>오렌지티비 대구동성로점</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="322">

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,22 +457,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>xcp_gn</t>
+          <t>pm_hd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>엑스케이프 강남점</t>
+          <t>파노라마 홍대입구점</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>xcp_gn</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>엑스케이프 강남점</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>xcr_kd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>엑스크라임 건대점</t>
         </is>
@@ -520,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C323"/>
+  <dimension ref="A1:C326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,12 +975,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>33_dj</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PLAY33 대전점</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -978,12 +990,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -993,12 +1005,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1008,12 +1020,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1023,12 +1035,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1038,12 +1050,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1053,12 +1065,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1068,12 +1080,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1083,12 +1095,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1098,12 +1110,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1113,12 +1125,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1128,12 +1140,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1143,12 +1155,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1158,12 +1170,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1173,12 +1185,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1188,12 +1200,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1203,12 +1215,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1218,12 +1230,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1233,12 +1245,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1248,12 +1260,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1263,12 +1275,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1278,12 +1290,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1293,12 +1305,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1308,12 +1320,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1323,12 +1335,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1338,12 +1350,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1353,12 +1365,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1368,12 +1380,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1383,12 +1395,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1398,12 +1410,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1413,12 +1425,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1428,12 +1440,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1443,16 +1455,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>33_dj</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
@@ -3783,12 +3795,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3798,12 +3810,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3813,12 +3825,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3828,12 +3840,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3843,12 +3855,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3858,12 +3870,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3873,12 +3885,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3888,12 +3900,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3903,12 +3915,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3918,12 +3930,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3933,12 +3945,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3948,12 +3960,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3963,12 +3975,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3978,12 +3990,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3993,12 +4005,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4008,12 +4020,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4023,12 +4035,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4038,12 +4050,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4053,12 +4065,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4068,12 +4080,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4083,12 +4095,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4098,12 +4110,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4113,12 +4125,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4128,12 +4140,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>tcd_sl</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>더 코드 신림점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4143,12 +4155,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4158,12 +4170,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>tcd_sl</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>더 코드 신림점</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4173,12 +4185,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4188,12 +4200,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4203,42 +4215,42 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C246" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C247" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4248,12 +4260,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4263,12 +4275,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4278,12 +4290,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4293,12 +4305,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4308,12 +4320,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4323,12 +4335,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4338,12 +4350,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4353,12 +4365,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4368,12 +4380,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4383,12 +4395,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4398,12 +4410,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4413,12 +4425,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4428,12 +4440,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4443,12 +4455,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4458,12 +4470,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4473,12 +4485,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4488,12 +4500,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4503,12 +4515,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4518,12 +4530,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4533,12 +4545,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4548,12 +4560,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4563,12 +4575,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4578,12 +4590,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4593,12 +4605,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4608,12 +4620,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4623,12 +4635,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4638,12 +4650,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4653,12 +4665,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4668,12 +4680,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4683,12 +4695,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>sh_nbc</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴부천점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4698,12 +4710,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4713,12 +4725,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4728,12 +4740,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4743,12 +4755,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4758,12 +4770,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4773,42 +4785,42 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C284" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C285" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4818,12 +4830,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4833,12 +4845,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>dia_mi</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>다이아에그 미스터리인</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4848,12 +4860,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4863,12 +4875,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>dia_mi</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>다이아에그 미스터리인</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4878,12 +4890,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4893,12 +4905,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4908,12 +4920,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4923,12 +4935,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4938,12 +4950,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4953,12 +4965,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4968,12 +4980,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4983,12 +4995,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4998,12 +5010,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5013,12 +5025,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5028,12 +5040,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5043,12 +5055,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5058,12 +5070,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5073,12 +5085,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5088,12 +5100,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5103,42 +5115,42 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C307" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5148,12 +5160,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5163,12 +5175,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5178,12 +5190,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5193,12 +5205,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5208,57 +5220,57 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>ser_dsr</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>서울이스케이프룸 대구동성로점</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5268,105 +5280,150 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>otv_dj</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>오렌지티비 대전은행점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>otv_dsr</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>오렌지티비 대구동성로점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>zw_gp</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>제로월드 김포본점</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
+          <t>otv_dj</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>오렌지티비 대전은행점</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>otv_dsr</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>오렌지티비 대구동성로점</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C323" t="n">
+      <c r="C326" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,34 +457,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pm_hd</t>
+          <t>xcp_gn</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>파노라마 홍대입구점</t>
+          <t>엑스케이프 강남점</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>xcp_gn</t>
+          <t>xcr_kd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
-        <is>
-          <t>엑스케이프 강남점</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>xcr_kd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
         <is>
           <t>엑스크라임 건대점</t>
         </is>
@@ -840,12 +828,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pm_hs</t>
+          <t>pm_hd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>파노라마 홍대삼거리점</t>
+          <t>파노라마 홍대입구점</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -855,12 +843,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pm_lw</t>
+          <t>pm_hs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>파노라마X롯데월드</t>
+          <t>파노라마 홍대삼거리점</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -870,12 +858,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qc_mk</t>
+          <t>pm_lw</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>퀘스천마크</t>
+          <t>파노라마X롯데월드</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -885,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>rle_sl2</t>
+          <t>qc_mk</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림2호점</t>
+          <t>퀘스천마크</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -900,12 +888,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rle_sl3</t>
+          <t>rle_sl2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림3호점</t>
+          <t>룸엘이스케이프 신림2호점</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -915,12 +903,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>se_ss</t>
+          <t>rle_sl3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>싸인이스케이프 상수점</t>
+          <t>룸엘이스케이프 신림3호점</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -930,12 +918,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>se_ss</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>싸인이스케이프 상수점</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -945,12 +933,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -960,12 +948,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -975,27 +963,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1005,12 +993,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1020,12 +1008,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1035,12 +1023,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1050,12 +1038,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1065,12 +1053,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1080,12 +1068,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1095,12 +1083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1110,12 +1098,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1125,12 +1113,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1140,12 +1128,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1155,12 +1143,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1170,12 +1158,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1185,12 +1173,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1200,12 +1188,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1215,12 +1203,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1230,12 +1218,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1245,12 +1233,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1260,12 +1248,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1275,12 +1263,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1290,12 +1278,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1305,12 +1293,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1320,12 +1308,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1335,12 +1323,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1350,12 +1338,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1365,12 +1353,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1380,12 +1368,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1395,12 +1383,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1410,12 +1398,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1425,12 +1413,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1440,12 +1428,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1455,27 +1443,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>33_dj</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PLAY33 대전점</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>33_kd</t>
+          <t>33_dj</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PLAY33 건대점</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1485,12 +1473,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>bp_ds</t>
+          <t>33_kd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>비트포비아 던전스텔라</t>
+          <t>PLAY33 건대점</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1500,12 +1488,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bp_sd</t>
+          <t>bp_ds</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전</t>
+          <t>비트포비아 던전스텔라</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1515,12 +1503,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ccr_1089</t>
+          <t>bp_sd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>쿠쿠룸 1089</t>
+          <t>비트포비아 서면던전</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1530,12 +1518,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>cd_ht</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>코드헌터 강남점</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1545,12 +1533,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cde_grs</t>
+          <t>cd_ht</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>코드이스케이프 가로수길점</t>
+          <t>코드헌터 강남점</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1560,12 +1548,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>clv_tw</t>
+          <t>cde_grs</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>클레버타운</t>
+          <t>코드이스케이프 가로수길점</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1575,12 +1563,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>d_coder</t>
+          <t>clv_tw</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Decoder</t>
+          <t>클레버타운</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1590,12 +1578,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>de_bp</t>
+          <t>d_coder</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>도어이스케이프 부평점</t>
+          <t>Decoder</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1605,12 +1593,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>de_sr</t>
+          <t>de_bp</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 레드점</t>
+          <t>도어이스케이프 부평점</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1620,12 +1608,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>de_sr</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>도어이스케이프 신논현 레드점</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1635,12 +1623,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ect_sc</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>이스케이프시티 그랜드 시티 신촌점</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1650,12 +1638,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>epsd_gn</t>
+          <t>ect_sc</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 강남점</t>
+          <t>이스케이프시티 그랜드 시티 신촌점</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1665,12 +1653,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1680,12 +1668,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1695,12 +1683,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>key_el</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>키이스케이프X에버랜드 메모리카니발</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1710,12 +1698,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>key_gn</t>
+          <t>key_el</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>키이스케이프 강남점</t>
+          <t>키이스케이프X에버랜드 메모리카니발</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1725,12 +1713,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>key_hd</t>
+          <t>key_gn</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>키이스케이프 홍대점</t>
+          <t>키이스케이프 강남점</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1740,12 +1728,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>key_hd</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>키이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1755,12 +1743,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1770,12 +1758,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1785,12 +1773,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1800,12 +1788,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1815,12 +1803,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1830,12 +1818,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1845,12 +1833,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1860,12 +1848,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1875,12 +1863,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1890,12 +1878,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1905,12 +1893,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>pnc_md</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>패닉이스케이프 목동점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1920,12 +1908,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>pnc_md</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>패닉이스케이프 목동점</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1935,12 +1923,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1950,12 +1938,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1965,12 +1953,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1980,12 +1968,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1995,12 +1983,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2010,12 +1998,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>sg_jj</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>비밀의 화원 전주점</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2025,12 +2013,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2040,12 +2028,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2055,12 +2043,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2070,12 +2058,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sv_kd1</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>솔버 1호점</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2085,12 +2073,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>sv_kd2</t>
+          <t>sv_kd1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>솔버 2호점</t>
+          <t>솔버 1호점</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2100,12 +2088,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sw_lab</t>
+          <t>sv_kd2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>수원방탈출연구소</t>
+          <t>솔버 2호점</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2115,12 +2103,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>sw_lab</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>수원방탈출연구소</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2130,12 +2118,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2145,27 +2133,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2175,12 +2163,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2190,12 +2178,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2205,12 +2193,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2220,12 +2208,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2235,12 +2223,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2250,12 +2238,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2265,12 +2253,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2280,12 +2268,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2295,12 +2283,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2310,12 +2298,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2325,12 +2313,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2340,12 +2328,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2355,12 +2343,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2370,12 +2358,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ect_bc</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>이스케이프시티 부천신중동점</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2385,12 +2373,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ep_lg</t>
+          <t>ect_bc</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>에필로그</t>
+          <t>이스케이프시티 부천신중동점</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2400,12 +2388,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>ep_lg</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>에필로그</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2415,12 +2403,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2430,12 +2418,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2445,12 +2433,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2460,12 +2448,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2475,12 +2463,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2490,12 +2478,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2505,12 +2493,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2520,12 +2508,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2535,12 +2523,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2550,12 +2538,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>머더파커 전주2호점</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2565,12 +2553,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2580,12 +2568,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2595,12 +2583,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2610,12 +2598,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2625,12 +2613,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2640,12 +2628,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2655,12 +2643,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2670,12 +2658,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2685,12 +2673,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2700,12 +2688,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2715,12 +2703,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2730,12 +2718,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2745,12 +2733,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2760,12 +2748,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2775,12 +2763,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2790,12 +2778,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2805,12 +2793,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2820,12 +2808,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2835,12 +2823,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2850,12 +2838,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2865,12 +2853,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2880,12 +2868,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2895,12 +2883,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2910,12 +2898,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2925,12 +2913,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2940,12 +2928,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2955,12 +2943,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2970,12 +2958,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2985,12 +2973,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3000,12 +2988,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3015,12 +3003,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3030,12 +3018,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3045,12 +3033,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3060,12 +3048,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3075,12 +3063,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3090,12 +3078,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3105,12 +3093,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3120,12 +3108,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3135,12 +3123,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3150,27 +3138,27 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3180,12 +3168,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3195,12 +3183,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3210,12 +3198,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>crew_sc2</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>탐정크루 신촌2호점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3225,12 +3213,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3240,12 +3228,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3255,12 +3243,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3270,12 +3258,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3285,12 +3273,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3300,12 +3288,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ect_sswu</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>이스케이프시티 성신여대점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3315,12 +3303,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3330,12 +3318,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3345,12 +3333,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>find_esc</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>더파인더 방탈출</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3360,12 +3348,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3375,12 +3363,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3390,12 +3378,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3405,12 +3393,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3420,12 +3408,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3435,12 +3423,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3450,12 +3438,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3465,12 +3453,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3480,12 +3468,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3495,12 +3483,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3510,12 +3498,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3525,12 +3513,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3540,12 +3528,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>머더파커 전주3호점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3555,12 +3543,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3570,12 +3558,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3585,12 +3573,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3600,12 +3588,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3615,12 +3603,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3630,12 +3618,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3645,12 +3633,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3660,12 +3648,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3675,12 +3663,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3690,12 +3678,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3705,12 +3693,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3720,12 +3708,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3735,12 +3723,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3750,12 +3738,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3765,12 +3753,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3780,12 +3768,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3795,12 +3783,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ser_bp</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부평점</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3810,12 +3798,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ser_sm</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부산서면점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3825,12 +3813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3840,12 +3828,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3855,12 +3843,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3870,12 +3858,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3885,12 +3873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3900,12 +3888,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3915,12 +3903,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3930,12 +3918,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3945,12 +3933,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3960,12 +3948,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3975,12 +3963,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3990,12 +3978,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4005,12 +3993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4020,12 +4008,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4035,12 +4023,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4050,12 +4038,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4065,12 +4053,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4080,12 +4068,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4095,12 +4083,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4110,12 +4098,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4125,12 +4113,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4140,12 +4128,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4155,12 +4143,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4170,12 +4158,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>tcd_sl</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>더 코드 신림점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C243" t="n">

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C326"/>
+  <dimension ref="A1:C328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,12 +723,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lt_ss</t>
+          <t>gk_ca</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>레토 성수</t>
+          <t>황금열쇠 천안아케이드점</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -738,12 +738,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>my_dam</t>
+          <t>lt_ss</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>미스터리 담</t>
+          <t>레토 성수</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -753,12 +753,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mz_gn</t>
+          <t>my_dam</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>괴담저장소 제일기숙학원</t>
+          <t>미스터리 담</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -768,12 +768,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mz_hd</t>
+          <t>mz_gn</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>괴담저장소 한강대 담력훈련</t>
+          <t>괴담저장소 제일기숙학원</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -783,12 +783,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ne_bnr</t>
+          <t>mz_hd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대 보네르관</t>
+          <t>괴담저장소 한강대 담력훈련</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -798,12 +798,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pa_hd</t>
+          <t>ne_bnr</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>플레이아레나 홍대점</t>
+          <t>넥스트에디션 건대 보네르관</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -813,12 +813,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pm_bs</t>
+          <t>pa_hd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>파노라마 부산점</t>
+          <t>플레이아레나 홍대점</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -828,12 +828,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pm_hd</t>
+          <t>pm_bs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>파노라마 홍대입구점</t>
+          <t>파노라마 부산점</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -843,12 +843,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pm_hs</t>
+          <t>pm_hd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>파노라마 홍대삼거리점</t>
+          <t>파노라마 홍대입구점</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -858,12 +858,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pm_lw</t>
+          <t>pm_hs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파노라마X롯데월드</t>
+          <t>파노라마 홍대삼거리점</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>qc_mk</t>
+          <t>pm_lw</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>퀘스천마크</t>
+          <t>파노라마X롯데월드</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -888,12 +888,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rle_sl2</t>
+          <t>qc_mk</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림2호점</t>
+          <t>퀘스천마크</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -903,12 +903,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rle_sl3</t>
+          <t>rle_sl2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림3호점</t>
+          <t>룸엘이스케이프 신림2호점</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -918,12 +918,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>se_ss</t>
+          <t>rle_sl3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>싸인이스케이프 상수점</t>
+          <t>룸엘이스케이프 신림3호점</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -933,12 +933,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>se_ss</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>싸인이스케이프 상수점</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -948,12 +948,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -963,12 +963,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -978,27 +978,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1008,12 +1008,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1023,12 +1023,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1038,12 +1038,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1053,12 +1053,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1068,12 +1068,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1083,12 +1083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1098,12 +1098,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1113,12 +1113,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1128,12 +1128,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1143,12 +1143,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1158,12 +1158,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1173,12 +1173,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1188,12 +1188,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1203,12 +1203,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1218,12 +1218,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1233,12 +1233,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1248,12 +1248,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1263,12 +1263,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1278,12 +1278,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1293,12 +1293,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1308,12 +1308,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1323,12 +1323,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1338,12 +1338,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1353,12 +1353,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1368,12 +1368,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1383,12 +1383,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1398,12 +1398,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1413,12 +1413,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1428,12 +1428,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1443,12 +1443,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1458,27 +1458,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>33_dj</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PLAY33 대전점</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>33_kd</t>
+          <t>33_dj</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PLAY33 건대점</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1488,12 +1488,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bp_ds</t>
+          <t>33_kd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>비트포비아 던전스텔라</t>
+          <t>PLAY33 건대점</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1503,12 +1503,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bp_sd</t>
+          <t>bp_ds</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전</t>
+          <t>비트포비아 던전스텔라</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1518,12 +1518,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ccr_1089</t>
+          <t>bp_sd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>쿠쿠룸 1089</t>
+          <t>비트포비아 서면던전</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1533,12 +1533,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cd_ht</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>코드헌터 강남점</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1548,12 +1548,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cde_grs</t>
+          <t>cd_ht</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>코드이스케이프 가로수길점</t>
+          <t>코드헌터 강남점</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1563,12 +1563,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>clv_tw</t>
+          <t>cde_grs</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>클레버타운</t>
+          <t>코드이스케이프 가로수길점</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1578,12 +1578,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>d_coder</t>
+          <t>clv_tw</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Decoder</t>
+          <t>클레버타운</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1593,12 +1593,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>de_bp</t>
+          <t>d_coder</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>도어이스케이프 부평점</t>
+          <t>Decoder</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1608,12 +1608,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>de_sr</t>
+          <t>de_bp</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 레드점</t>
+          <t>도어이스케이프 부평점</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1623,12 +1623,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>de_sr</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>도어이스케이프 신논현 레드점</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1638,12 +1638,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ect_sc</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>이스케이프시티 그랜드 시티 신촌점</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1653,12 +1653,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>epsd_gn</t>
+          <t>ect_sc</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 강남점</t>
+          <t>이스케이프시티 그랜드 시티 신촌점</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1668,12 +1668,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1683,12 +1683,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1698,12 +1698,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>key_el</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>키이스케이프X에버랜드 메모리카니발</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1713,12 +1713,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>key_gn</t>
+          <t>key_el</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>키이스케이프 강남점</t>
+          <t>키이스케이프X에버랜드 메모리카니발</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1728,12 +1728,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>key_hd</t>
+          <t>key_gn</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>키이스케이프 홍대점</t>
+          <t>키이스케이프 강남점</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1743,12 +1743,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>key_hd</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>키이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1758,12 +1758,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1773,12 +1773,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1788,12 +1788,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1803,12 +1803,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1818,12 +1818,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1833,12 +1833,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1848,12 +1848,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1863,12 +1863,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1878,12 +1878,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1893,12 +1893,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1908,12 +1908,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>pnc_md</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>패닉이스케이프 목동점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1923,12 +1923,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>pnc_md</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>패닉이스케이프 목동점</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1938,12 +1938,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1953,12 +1953,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1968,12 +1968,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1983,12 +1983,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1998,12 +1998,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2013,12 +2013,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>sg_jj</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>비밀의 화원 전주점</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2028,12 +2028,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2043,12 +2043,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2058,12 +2058,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2073,12 +2073,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>sv_kd1</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>솔버 1호점</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2088,12 +2088,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sv_kd2</t>
+          <t>sv_kd1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>솔버 2호점</t>
+          <t>솔버 1호점</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2103,12 +2103,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sw_lab</t>
+          <t>sv_kd2</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>수원방탈출연구소</t>
+          <t>솔버 2호점</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -3063,12 +3063,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>sw_lab</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>수원방탈출연구소</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3078,12 +3078,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3093,12 +3093,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3108,12 +3108,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3123,12 +3123,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3138,12 +3138,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3153,27 +3153,27 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3183,12 +3183,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3198,12 +3198,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3213,12 +3213,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>crew_sc2</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>탐정크루 신촌2호점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3228,12 +3228,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3243,12 +3243,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3258,12 +3258,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3273,12 +3273,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3288,12 +3288,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3303,12 +3303,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ect_sswu</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>이스케이프시티 성신여대점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3318,12 +3318,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3333,12 +3333,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3348,12 +3348,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>find_esc</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>더파인더 방탈출</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3363,12 +3363,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3378,12 +3378,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3393,12 +3393,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3408,12 +3408,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3423,12 +3423,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3438,12 +3438,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3453,12 +3453,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3468,12 +3468,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3483,12 +3483,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3498,12 +3498,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3513,12 +3513,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3528,12 +3528,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3543,12 +3543,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>머더파커 전주3호점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3558,12 +3558,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3573,12 +3573,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3588,12 +3588,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3603,12 +3603,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3618,12 +3618,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3633,12 +3633,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3648,12 +3648,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3663,12 +3663,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3678,12 +3678,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3693,12 +3693,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3708,12 +3708,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3723,12 +3723,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3738,12 +3738,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3753,12 +3753,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3768,12 +3768,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3783,12 +3783,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3798,12 +3798,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ser_bp</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부평점</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3813,12 +3813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ser_sm</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부산서면점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3828,12 +3828,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3843,12 +3843,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3858,12 +3858,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3873,12 +3873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3888,12 +3888,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3903,12 +3903,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3918,12 +3918,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3933,12 +3933,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3948,12 +3948,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3963,12 +3963,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3978,12 +3978,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3993,12 +3993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4008,12 +4008,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4023,12 +4023,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4038,12 +4038,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4053,12 +4053,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4068,12 +4068,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4083,12 +4083,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4098,12 +4098,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4113,12 +4113,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4128,12 +4128,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4143,12 +4143,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_yb</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 역북점 (T.A)</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4158,12 +4158,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4173,12 +4173,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4188,12 +4188,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4203,12 +4203,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4218,12 +4218,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4233,42 +4233,42 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C248" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4278,12 +4278,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4293,12 +4293,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4308,12 +4308,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4323,12 +4323,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4338,12 +4338,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4353,12 +4353,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4368,12 +4368,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4383,12 +4383,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4398,12 +4398,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4413,12 +4413,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4428,12 +4428,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4443,12 +4443,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4458,12 +4458,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4473,12 +4473,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4488,12 +4488,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4503,12 +4503,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4518,12 +4518,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4533,12 +4533,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4548,12 +4548,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4563,12 +4563,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4578,12 +4578,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4593,12 +4593,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4608,12 +4608,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4623,12 +4623,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4638,12 +4638,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4653,12 +4653,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4668,12 +4668,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4683,12 +4683,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4698,12 +4698,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4713,12 +4713,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>sh_nbc</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴부천점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4728,12 +4728,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4743,12 +4743,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4758,12 +4758,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4773,12 +4773,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4788,12 +4788,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4803,42 +4803,42 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C286" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4848,12 +4848,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4863,12 +4863,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>dia_mi</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>다이아에그 미스터리인</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4878,12 +4878,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4893,12 +4893,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>dia_mi</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>다이아에그 미스터리인</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4908,12 +4908,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4923,12 +4923,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4938,12 +4938,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4953,12 +4953,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4968,12 +4968,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4983,12 +4983,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4998,12 +4998,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5013,12 +5013,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5028,12 +5028,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5043,12 +5043,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5058,12 +5058,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5073,12 +5073,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5088,12 +5088,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5103,12 +5103,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5118,12 +5118,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5133,42 +5133,42 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C308" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5178,12 +5178,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5193,12 +5193,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5208,12 +5208,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ser_dsr</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 대구동성로점</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5223,12 +5223,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5238,12 +5238,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>ser_dsr</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>서울이스케이프룸 대구동성로점</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5253,42 +5253,42 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5298,12 +5298,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5313,105 +5313,135 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>otv_dj</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>오렌지티비 대전은행점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>otv_dsr</t>
+          <t>zw_gp</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>오렌지티비 대구동성로점</t>
+          <t>제로월드 김포본점</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>otv_dj</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>오렌지티비 대전은행점</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
+          <t>otv_dsr</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>오렌지티비 대구동성로점</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C326" t="n">
+      <c r="C328" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C328"/>
+  <dimension ref="A1:C332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dp_tk</t>
+          <t>dia_cafe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>딥띵커</t>
+          <t>다이아에그 3호점 육향찻집</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -648,12 +648,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>dp_tk</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>딥띵커</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -663,12 +663,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>etp_d</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엔터팟 1호점</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -678,12 +678,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ft_str1</t>
+          <t>etp_d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>판타스트릭 1호점</t>
+          <t>엔터팟 1호점</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -693,12 +693,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ft_str2</t>
+          <t>ft_str1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>판타스트릭 2호점</t>
+          <t>판타스트릭 1호점</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -708,12 +708,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ft_str3</t>
+          <t>ft_str2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>판타스트릭 TGC</t>
+          <t>판타스트릭 2호점</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -753,12 +753,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>my_dam</t>
+          <t>mhz_esc</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>미스터리 담</t>
+          <t>MHZ ESCAPE</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -768,12 +768,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mz_gn</t>
+          <t>my_dam</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>괴담저장소 제일기숙학원</t>
+          <t>미스터리 담</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -783,12 +783,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mz_hd</t>
+          <t>mz_gn</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>괴담저장소 한강대 담력훈련</t>
+          <t>괴담저장소 제일기숙학원</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -798,12 +798,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ne_bnr</t>
+          <t>mz_hd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대 보네르관</t>
+          <t>괴담저장소 한강대 담력훈련</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -813,12 +813,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pa_hd</t>
+          <t>ne_bnr</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>플레이아레나 홍대점</t>
+          <t>넥스트에디션 건대 보네르관</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -828,12 +828,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pm_bs</t>
+          <t>pa_hd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>파노라마 부산점</t>
+          <t>플레이아레나 홍대점</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -843,12 +843,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pm_hd</t>
+          <t>plus_esc</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>파노라마 홍대입구점</t>
+          <t>플러스 이스케이프</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -858,12 +858,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pm_hs</t>
+          <t>pm_bs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파노라마 홍대삼거리점</t>
+          <t>파노라마 부산점</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pm_lw</t>
+          <t>pm_hd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>파노라마X롯데월드</t>
+          <t>파노라마 홍대입구점</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -888,12 +888,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>qc_mk</t>
+          <t>pm_hs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>퀘스천마크</t>
+          <t>파노라마 홍대삼거리점</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -903,12 +903,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rle_sl2</t>
+          <t>pm_lw</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림2호점</t>
+          <t>파노라마X롯데월드</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -918,12 +918,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rle_sl3</t>
+          <t>qc_mk</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림3호점</t>
+          <t>퀘스천마크</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -933,12 +933,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>se_ss</t>
+          <t>rle_sl2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>싸인이스케이프 상수점</t>
+          <t>룸엘이스케이프 신림2호점</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -948,12 +948,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>rle_sl3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>룸엘이스케이프 신림3호점</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -963,12 +963,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>se_ss</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>싸인이스케이프 상수점</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -978,12 +978,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -993,42 +993,42 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1038,12 +1038,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1053,12 +1053,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1068,12 +1068,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1083,12 +1083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1098,12 +1098,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1113,12 +1113,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1128,12 +1128,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1143,12 +1143,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1158,12 +1158,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>ft_str3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>판타스트릭 TGC</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1173,12 +1173,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1188,12 +1188,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1203,12 +1203,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1218,12 +1218,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1233,12 +1233,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1248,12 +1248,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1263,12 +1263,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1278,12 +1278,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1293,12 +1293,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1308,12 +1308,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1323,12 +1323,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1338,12 +1338,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1353,12 +1353,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1368,12 +1368,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1383,12 +1383,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1398,12 +1398,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1413,12 +1413,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1428,12 +1428,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1443,12 +1443,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1458,12 +1458,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1473,57 +1473,57 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>33_dj</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PLAY33 대전점</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>33_kd</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PLAY33 건대점</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>bp_ds</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>비트포비아 던전스텔라</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bp_sd</t>
+          <t>33_dj</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1533,12 +1533,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ccr_1089</t>
+          <t>33_kd</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>쿠쿠룸 1089</t>
+          <t>PLAY33 건대점</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1548,12 +1548,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cd_ht</t>
+          <t>bp_ds</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>코드헌터 강남점</t>
+          <t>비트포비아 던전스텔라</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1563,12 +1563,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cde_grs</t>
+          <t>bp_sd</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>코드이스케이프 가로수길점</t>
+          <t>비트포비아 서면던전</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1578,12 +1578,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>clv_tw</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>클레버타운</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1593,12 +1593,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>d_coder</t>
+          <t>cd_ht</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Decoder</t>
+          <t>코드헌터 강남점</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1608,12 +1608,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>de_bp</t>
+          <t>cde_grs</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>도어이스케이프 부평점</t>
+          <t>코드이스케이프 가로수길점</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1623,12 +1623,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>de_sr</t>
+          <t>clv_tw</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 레드점</t>
+          <t>클레버타운</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1638,12 +1638,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>d_coder</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>Decoder</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1653,12 +1653,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ect_sc</t>
+          <t>de_bp</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>이스케이프시티 그랜드 시티 신촌점</t>
+          <t>도어이스케이프 부평점</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1668,12 +1668,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>epsd_gn</t>
+          <t>de_sr</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 강남점</t>
+          <t>도어이스케이프 신논현 레드점</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1683,12 +1683,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1698,12 +1698,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>dm_fear</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>둠이스케이프 FEAR점</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1713,12 +1713,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>key_el</t>
+          <t>ect_sc</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>키이스케이프X에버랜드 메모리카니발</t>
+          <t>이스케이프시티 그랜드 시티 신촌점</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1728,12 +1728,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>key_gn</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>키이스케이프 강남점</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1743,12 +1743,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>key_hd</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>키이스케이프 홍대점</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1758,12 +1758,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1773,12 +1773,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_el</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프X에버랜드 메모리카니발</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1788,12 +1788,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>key_gn</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>키이스케이프 강남점</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1803,12 +1803,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>key_hd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>키이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1818,12 +1818,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1833,12 +1833,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1848,12 +1848,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1863,12 +1863,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1878,12 +1878,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1893,12 +1893,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1908,12 +1908,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1923,12 +1923,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>pnc_md</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>패닉이스케이프 목동점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1938,12 +1938,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1953,12 +1953,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1968,12 +1968,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1983,12 +1983,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>pnc_md</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>패닉이스케이프 목동점</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1998,12 +1998,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2013,12 +2013,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2028,12 +2028,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>sg_jj</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>비밀의 화원 전주점</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2043,12 +2043,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2058,12 +2058,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2073,12 +2073,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2088,12 +2088,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sv_kd1</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>솔버 1호점</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2103,12 +2103,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sv_kd2</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>솔버 2호점</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2118,12 +2118,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2133,12 +2133,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2148,72 +2148,72 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>sv_kd1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>솔버 1호점</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>sv_kd2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>솔버 2호점</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2223,12 +2223,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2238,12 +2238,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2253,12 +2253,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2268,12 +2268,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2283,12 +2283,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2298,12 +2298,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2313,12 +2313,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2328,12 +2328,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2343,12 +2343,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>다이아에그 1호점 부산서면점</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2358,12 +2358,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2373,12 +2373,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ect_bc</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>이스케이프시티 부천신중동점</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2388,12 +2388,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ep_lg</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>에필로그</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2403,12 +2403,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2418,12 +2418,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2433,12 +2433,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>ect_bc</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>이스케이프시티 부천신중동점</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2448,12 +2448,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>ep_lg</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>에필로그</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2463,12 +2463,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2478,12 +2478,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2493,12 +2493,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2508,12 +2508,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2523,12 +2523,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2538,12 +2538,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2553,12 +2553,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2568,12 +2568,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2583,12 +2583,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2598,12 +2598,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>머더파커 전주2호점</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2613,12 +2613,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2628,12 +2628,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2643,12 +2643,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2658,12 +2658,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2673,12 +2673,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2688,12 +2688,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2703,12 +2703,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2718,12 +2718,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2733,12 +2733,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2748,12 +2748,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2763,12 +2763,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2778,12 +2778,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2793,12 +2793,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2808,12 +2808,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2823,12 +2823,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2838,12 +2838,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2853,12 +2853,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2868,12 +2868,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2883,12 +2883,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2898,12 +2898,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2913,12 +2913,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2928,12 +2928,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2943,12 +2943,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2958,12 +2958,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2973,12 +2973,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2988,12 +2988,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3003,12 +3003,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3018,12 +3018,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3033,12 +3033,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3048,12 +3048,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3063,12 +3063,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>sw_lab</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>수원방탈출연구소</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3078,12 +3078,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3093,12 +3093,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3108,12 +3108,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3123,12 +3123,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>sw_lab</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>수원방탈출연구소</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3138,12 +3138,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3153,12 +3153,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3168,72 +3168,72 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>crew_sc2</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>탐정크루 신촌2호점</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3243,12 +3243,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3258,12 +3258,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3273,12 +3273,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3288,12 +3288,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3303,12 +3303,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3318,12 +3318,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ect_sswu</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>이스케이프시티 성신여대점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3333,12 +3333,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3348,12 +3348,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3363,12 +3363,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>find_esc</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>더파인더 방탈출</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3378,12 +3378,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3393,12 +3393,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3408,12 +3408,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3423,12 +3423,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3438,12 +3438,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3453,12 +3453,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3468,12 +3468,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3483,12 +3483,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3498,12 +3498,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3513,12 +3513,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3528,12 +3528,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3543,12 +3543,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3558,12 +3558,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3573,12 +3573,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3588,12 +3588,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3603,12 +3603,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>머더파커 전주3호점</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3618,12 +3618,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3633,12 +3633,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3648,12 +3648,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3663,12 +3663,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3678,12 +3678,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3693,12 +3693,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3708,12 +3708,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3723,12 +3723,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3738,12 +3738,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3753,12 +3753,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3768,12 +3768,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3783,12 +3783,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3798,12 +3798,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3813,12 +3813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ser_bp</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부평점</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3828,12 +3828,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ser_sm</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부산서면점</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3843,12 +3843,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3858,12 +3858,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3873,12 +3873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3888,12 +3888,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3903,12 +3903,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3918,12 +3918,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3933,12 +3933,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3948,12 +3948,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3963,12 +3963,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3978,12 +3978,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3993,12 +3993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4008,12 +4008,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4023,12 +4023,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4038,12 +4038,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4053,12 +4053,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4068,12 +4068,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4083,12 +4083,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4098,12 +4098,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4113,12 +4113,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4128,12 +4128,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4143,12 +4143,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>sh_yb</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>셜록홈즈 역북점 (T.A)</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4158,12 +4158,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4173,12 +4173,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4188,12 +4188,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4203,12 +4203,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>sh_yb</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>셜록홈즈 역북점 (T.A)</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4218,12 +4218,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4233,12 +4233,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4248,12 +4248,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4263,72 +4263,72 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C250" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C252" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4338,12 +4338,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4353,12 +4353,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4368,12 +4368,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4383,12 +4383,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4398,12 +4398,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4413,12 +4413,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4428,12 +4428,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4443,12 +4443,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4458,12 +4458,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4473,12 +4473,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4488,12 +4488,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4503,12 +4503,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4518,12 +4518,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4533,12 +4533,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4548,12 +4548,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4563,12 +4563,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4578,12 +4578,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4593,12 +4593,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4608,12 +4608,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4623,12 +4623,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4638,12 +4638,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4653,12 +4653,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4668,12 +4668,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4683,12 +4683,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4698,12 +4698,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4713,12 +4713,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4728,12 +4728,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4743,12 +4743,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sh_nbc</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴부천점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4758,12 +4758,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4773,12 +4773,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4788,12 +4788,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4803,12 +4803,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4818,12 +4818,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4833,72 +4833,72 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C288" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C289" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C290" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C291" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>dia_mi</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>다이아에그 미스터리인</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4908,12 +4908,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4923,12 +4923,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4938,12 +4938,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4953,12 +4953,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>dia_mi</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>다이아에그 2호점 미스테리인</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4968,12 +4968,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4983,12 +4983,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4998,12 +4998,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5013,12 +5013,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5028,12 +5028,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5043,12 +5043,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5058,12 +5058,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5073,12 +5073,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5088,12 +5088,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5103,12 +5103,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5118,12 +5118,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5133,12 +5133,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5148,12 +5148,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5163,72 +5163,72 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C311" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C313" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5238,12 +5238,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ser_dsr</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 대구동성로점</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5253,12 +5253,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5268,12 +5268,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5283,165 +5283,225 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>ser_dsr</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>서울이스케이프룸 대구동성로점</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>otv_dj</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>오렌지티비 대전은행점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>otv_dsr</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>오렌지티비 대구동성로점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
+          <t>zw_gp</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>제로월드 김포본점</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>otv_dj</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>오렌지티비 대전은행점</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>otv_dsr</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>오렌지티비 대구동성로점</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C328" t="n">
+      <c r="C332" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -2298,12 +2298,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2313,12 +2313,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2328,12 +2328,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>다이아에그 1호점 부산서면점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2343,12 +2343,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>다이아에그 1호점 부산서면점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2358,12 +2358,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2373,12 +2373,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2388,12 +2388,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2403,12 +2403,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2418,12 +2418,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>ect_bc</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>이스케이프시티 부천신중동점</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2433,12 +2433,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ect_bc</t>
+          <t>ep_lg</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>이스케이프시티 부천신중동점</t>
+          <t>에필로그</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2448,12 +2448,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ep_lg</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>에필로그</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2463,12 +2463,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2478,12 +2478,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2493,12 +2493,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2508,12 +2508,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2523,12 +2523,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2538,12 +2538,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2553,12 +2553,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2568,12 +2568,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2583,12 +2583,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>머더파커 전주2호점</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2598,12 +2598,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2613,12 +2613,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2628,12 +2628,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2643,12 +2643,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2658,12 +2658,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2673,12 +2673,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2688,12 +2688,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2703,12 +2703,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2718,12 +2718,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2733,12 +2733,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2748,12 +2748,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2763,12 +2763,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2778,12 +2778,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2793,12 +2793,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2808,12 +2808,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2823,12 +2823,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2838,12 +2838,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2853,12 +2853,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2868,12 +2868,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2883,12 +2883,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2898,12 +2898,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2913,12 +2913,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2928,12 +2928,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2943,12 +2943,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2958,12 +2958,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2973,12 +2973,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2988,12 +2988,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3003,12 +3003,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3018,12 +3018,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3033,12 +3033,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3048,12 +3048,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3063,12 +3063,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3078,12 +3078,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3093,12 +3093,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3108,12 +3108,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sw_lab</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>수원방탈출연구소</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3123,12 +3123,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>sw_lab</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>수원방탈출연구소</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3138,12 +3138,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3153,12 +3153,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3168,12 +3168,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3183,12 +3183,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3198,12 +3198,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3213,27 +3213,27 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3243,12 +3243,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3258,12 +3258,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3273,12 +3273,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3288,12 +3288,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>crew_sc2</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>탐정크루 신촌2호점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C185" t="n">

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -3288,12 +3288,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3303,12 +3303,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3318,12 +3318,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3333,12 +3333,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3348,12 +3348,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3363,12 +3363,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3378,12 +3378,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ect_sswu</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>이스케이프시티 성신여대점</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3393,12 +3393,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3408,12 +3408,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3423,12 +3423,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>find_esc</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>더파인더 방탈출</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3438,12 +3438,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3453,12 +3453,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3468,12 +3468,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3483,12 +3483,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3498,12 +3498,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3513,12 +3513,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3528,12 +3528,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3543,12 +3543,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3558,12 +3558,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3573,12 +3573,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3588,12 +3588,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>머더파커 전주3호점</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3603,12 +3603,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3618,12 +3618,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3633,12 +3633,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3648,12 +3648,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3663,12 +3663,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3678,12 +3678,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3693,12 +3693,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3708,12 +3708,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3723,12 +3723,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3738,12 +3738,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3753,12 +3753,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3768,12 +3768,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3783,12 +3783,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3798,12 +3798,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3813,12 +3813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3828,12 +3828,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3843,12 +3843,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3858,12 +3858,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3873,12 +3873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ser_bp</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부평점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3888,12 +3888,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ser_sm</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부산서면점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3903,12 +3903,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3918,12 +3918,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3933,12 +3933,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3948,12 +3948,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3963,12 +3963,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3978,12 +3978,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3993,12 +3993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4008,12 +4008,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4023,12 +4023,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4038,12 +4038,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4053,12 +4053,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4068,12 +4068,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4083,12 +4083,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4098,12 +4098,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4113,12 +4113,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4128,12 +4128,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4143,12 +4143,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4158,12 +4158,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4173,12 +4173,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4188,12 +4188,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_yb</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 역북점 (T.A)</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4203,12 +4203,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>sh_yb</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>셜록홈즈 역북점 (T.A)</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4218,12 +4218,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4233,12 +4233,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4248,12 +4248,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4263,12 +4263,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4278,12 +4278,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4293,12 +4293,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4308,27 +4308,27 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4338,12 +4338,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4353,12 +4353,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4368,12 +4368,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4383,12 +4383,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C258" t="n">

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -633,12 +633,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dia_cafe</t>
+          <t>dp_tk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이아에그 3호점 육향찻집</t>
+          <t>딥띵커</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -648,12 +648,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dp_tk</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>딥띵커</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -663,12 +663,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>etp_d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>엔터팟 1호점</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -678,12 +678,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>etp_d</t>
+          <t>ft_str1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엔터팟 1호점</t>
+          <t>판타스트릭 1호점</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -693,12 +693,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ft_str1</t>
+          <t>ft_str2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>판타스트릭 1호점</t>
+          <t>판타스트릭 2호점</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -708,12 +708,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ft_str2</t>
+          <t>gk_ca</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>판타스트릭 2호점</t>
+          <t>황금열쇠 천안아케이드점</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -723,12 +723,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gk_ca</t>
+          <t>lt_ss</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>황금열쇠 천안아케이드점</t>
+          <t>레토 성수</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -738,12 +738,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lt_ss</t>
+          <t>mhz_esc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>레토 성수</t>
+          <t>MHZ ESCAPE</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -753,12 +753,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mhz_esc</t>
+          <t>my_dam</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MHZ ESCAPE</t>
+          <t>미스터리 담</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -768,12 +768,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>my_dam</t>
+          <t>mz_gn</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>미스터리 담</t>
+          <t>괴담저장소 제일기숙학원</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -783,12 +783,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mz_gn</t>
+          <t>mz_hd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>괴담저장소 제일기숙학원</t>
+          <t>괴담저장소 한강대 담력훈련</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -798,12 +798,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mz_hd</t>
+          <t>ne_bnr</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>괴담저장소 한강대 담력훈련</t>
+          <t>넥스트에디션 건대 보네르관</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -813,12 +813,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ne_bnr</t>
+          <t>pa_hd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대 보네르관</t>
+          <t>플레이아레나 홍대점</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -828,12 +828,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pa_hd</t>
+          <t>plus_esc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>플레이아레나 홍대점</t>
+          <t>플러스 이스케이프</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -843,12 +843,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>plus_esc</t>
+          <t>pm_bs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>플러스 이스케이프</t>
+          <t>파노라마 부산점</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -858,12 +858,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pm_bs</t>
+          <t>pm_hd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파노라마 부산점</t>
+          <t>파노라마 홍대입구점</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pm_hd</t>
+          <t>pm_hs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>파노라마 홍대입구점</t>
+          <t>파노라마 홍대삼거리점</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -888,12 +888,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pm_hs</t>
+          <t>pm_lw</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>파노라마 홍대삼거리점</t>
+          <t>파노라마X롯데월드</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -903,12 +903,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pm_lw</t>
+          <t>qc_mk</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>파노라마X롯데월드</t>
+          <t>퀘스천마크</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -918,12 +918,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qc_mk</t>
+          <t>rle_sl2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>퀘스천마크</t>
+          <t>룸엘이스케이프 신림2호점</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -933,12 +933,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rle_sl2</t>
+          <t>rle_sl3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림2호점</t>
+          <t>룸엘이스케이프 신림3호점</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -948,12 +948,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>rle_sl3</t>
+          <t>se_ss</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림3호점</t>
+          <t>싸인이스케이프 상수점</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -963,12 +963,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>se_ss</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>싸인이스케이프 상수점</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -978,12 +978,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -993,12 +993,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1008,27 +1008,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1038,12 +1038,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1053,12 +1053,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1068,12 +1068,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1083,12 +1083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1098,12 +1098,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>dia_town</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>다이아에그 미스테리타운</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1368,12 +1368,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1383,12 +1383,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1398,12 +1398,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1413,12 +1413,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1428,12 +1428,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1443,12 +1443,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1458,12 +1458,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1473,12 +1473,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1488,12 +1488,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1503,27 +1503,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>33_dj</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>33_dj</t>
+          <t>33_kd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PLAY33 대전점</t>
+          <t>PLAY33 건대점</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1533,12 +1533,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>33_kd</t>
+          <t>bp_ds</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PLAY33 건대점</t>
+          <t>비트포비아 던전스텔라</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1548,12 +1548,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bp_ds</t>
+          <t>bp_sd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>비트포비아 던전스텔라</t>
+          <t>비트포비아 서면던전</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1563,12 +1563,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>bp_sd</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1578,12 +1578,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ccr_1089</t>
+          <t>cd_ht</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>쿠쿠룸 1089</t>
+          <t>코드헌터 강남점</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1593,12 +1593,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cd_ht</t>
+          <t>cde_grs</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>코드헌터 강남점</t>
+          <t>코드이스케이프 가로수길점</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1608,12 +1608,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>cde_grs</t>
+          <t>clv_tw</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>코드이스케이프 가로수길점</t>
+          <t>클레버타운</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1623,12 +1623,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>clv_tw</t>
+          <t>d_coder</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>클레버타운</t>
+          <t>Decoder</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1638,12 +1638,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>d_coder</t>
+          <t>de_bp</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Decoder</t>
+          <t>도어이스케이프 부평점</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1653,12 +1653,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>de_bp</t>
+          <t>de_sr</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>도어이스케이프 부평점</t>
+          <t>도어이스케이프 신논현 레드점</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1668,12 +1668,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>de_sr</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 레드점</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1683,12 +1683,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>dm_fear</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>둠이스케이프 FEAR점</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1698,12 +1698,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dm_fear</t>
+          <t>ect_sc</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>둠이스케이프 FEAR점</t>
+          <t>이스케이프시티 그랜드 시티 신촌점</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1713,12 +1713,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ect_sc</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>이스케이프시티 그랜드 시티 신촌점</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1728,12 +1728,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>epsd_gn</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 강남점</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1743,12 +1743,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1758,12 +1758,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>key_el</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>키이스케이프X에버랜드 메모리카니발</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1773,12 +1773,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>key_el</t>
+          <t>key_gn</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>키이스케이프X에버랜드 메모리카니발</t>
+          <t>키이스케이프 강남점</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1788,12 +1788,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>key_gn</t>
+          <t>key_hd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>키이스케이프 강남점</t>
+          <t>키이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1803,12 +1803,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>key_hd</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>키이스케이프 홍대점</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1818,12 +1818,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1833,12 +1833,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1848,12 +1848,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1863,12 +1863,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1878,12 +1878,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1893,12 +1893,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1908,12 +1908,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1923,12 +1923,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1938,12 +1938,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1953,12 +1953,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1968,12 +1968,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>pnc_md</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>패닉이스케이프 목동점</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1983,12 +1983,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>pnc_md</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>패닉이스케이프 목동점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1998,12 +1998,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2013,12 +2013,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2028,12 +2028,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>다이아에그 1호점 부산서면점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>셜록홈즈 역북점 (T.A)</t>
+          <t>셜록홈즈 용인역북점 (T.A)</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4953,12 +4953,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>dia_mi</t>
+          <t>dia_inn</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>다이아에그 2호점 미스테리인</t>
+          <t>다이아에그 미스테리인</t>
         </is>
       </c>
       <c r="C296" t="n">

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C332"/>
+  <dimension ref="A1:C335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1908,12 +1908,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>mp_kd2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>머더파커 건대2호점</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1923,12 +1923,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1938,12 +1938,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1953,12 +1953,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1968,12 +1968,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>pnc_md</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>패닉이스케이프 목동점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1983,12 +1983,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>pnc_md</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>패닉이스케이프 목동점</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1998,12 +1998,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2013,12 +2013,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2028,12 +2028,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2043,12 +2043,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2058,12 +2058,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2073,12 +2073,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2088,12 +2088,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sg_jj</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>비밀의 화원 전주점</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2103,12 +2103,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2118,12 +2118,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2133,12 +2133,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2148,12 +2148,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sv_kd1</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>솔버 1호점</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2163,12 +2163,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sv_kd2</t>
+          <t>sv_kd1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>솔버 2호점</t>
+          <t>솔버 1호점</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2178,12 +2178,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>sv_kd2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>솔버 2호점</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2193,12 +2193,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2208,27 +2208,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2238,12 +2238,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2253,12 +2253,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2268,12 +2268,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2283,12 +2283,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2298,12 +2298,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2313,12 +2313,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2328,12 +2328,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2343,12 +2343,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2358,12 +2358,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2373,12 +2373,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2388,12 +2388,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2403,12 +2403,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2418,12 +2418,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ect_bc</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>이스케이프시티 부천신중동점</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2433,12 +2433,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ep_lg</t>
+          <t>ect_bc</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>에필로그</t>
+          <t>이스케이프시티 부천신중동점</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2448,12 +2448,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>ep_lg</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>에필로그</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2463,12 +2463,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2478,12 +2478,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>gom_sm</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>게임 오브 마인드 서면점</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2493,12 +2493,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2508,12 +2508,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2523,12 +2523,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2538,12 +2538,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2553,12 +2553,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2568,12 +2568,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2583,12 +2583,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2598,12 +2598,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2613,12 +2613,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>머더파커 전주2호점 어드벤처</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2628,12 +2628,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2643,12 +2643,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2658,12 +2658,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2673,12 +2673,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2688,12 +2688,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2703,12 +2703,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2718,12 +2718,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2733,12 +2733,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2748,12 +2748,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2763,12 +2763,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2778,12 +2778,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2793,12 +2793,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2808,12 +2808,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2823,12 +2823,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2838,12 +2838,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2853,12 +2853,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2868,12 +2868,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2883,12 +2883,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2898,12 +2898,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2913,12 +2913,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2928,12 +2928,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2943,12 +2943,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2958,12 +2958,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2973,12 +2973,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2988,12 +2988,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3003,12 +3003,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3018,12 +3018,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3033,12 +3033,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3048,12 +3048,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3063,12 +3063,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3078,12 +3078,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3093,12 +3093,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3108,12 +3108,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>sw_lab</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>수원방탈출연구소</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3123,12 +3123,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3138,12 +3138,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>sw_lab</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>수원방탈출연구소</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3153,12 +3153,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3168,12 +3168,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3183,12 +3183,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3198,12 +3198,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3213,42 +3213,42 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3258,12 +3258,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3273,12 +3273,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>crew_sc2</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>탐정크루 신촌2호점</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3288,12 +3288,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3303,12 +3303,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3318,12 +3318,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3333,12 +3333,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3348,12 +3348,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3363,12 +3363,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ect_sswu</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>이스케이프시티 성신여대점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3378,12 +3378,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3393,12 +3393,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3408,12 +3408,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>find_esc</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>더파인더 방탈출</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3423,12 +3423,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3438,12 +3438,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3453,12 +3453,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3468,12 +3468,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3483,12 +3483,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3498,12 +3498,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3513,12 +3513,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3528,12 +3528,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3543,12 +3543,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3558,12 +3558,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3573,12 +3573,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3588,12 +3588,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3603,12 +3603,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3618,12 +3618,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>머더파커 전주3호점 E.T</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3633,12 +3633,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3648,12 +3648,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3663,12 +3663,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3678,12 +3678,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3693,12 +3693,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3708,12 +3708,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3723,12 +3723,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3738,12 +3738,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3753,12 +3753,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3768,12 +3768,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3783,12 +3783,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3798,12 +3798,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3813,12 +3813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3828,12 +3828,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3843,12 +3843,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3858,12 +3858,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ser_bp</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부평점</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3873,12 +3873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ser_sm</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부산서면점</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3888,12 +3888,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3903,12 +3903,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3918,12 +3918,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3933,12 +3933,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3948,12 +3948,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3963,12 +3963,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3978,12 +3978,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3993,12 +3993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4008,12 +4008,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4023,12 +4023,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4038,12 +4038,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4053,12 +4053,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4068,12 +4068,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4083,12 +4083,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4098,12 +4098,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4113,12 +4113,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4128,12 +4128,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4143,12 +4143,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4158,12 +4158,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4173,12 +4173,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4188,12 +4188,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>sh_yb</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인역북점 (T.A)</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4203,12 +4203,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4218,12 +4218,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_yb</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 용인역북점 (T.A)</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4233,12 +4233,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4248,12 +4248,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4263,12 +4263,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4278,12 +4278,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4293,12 +4293,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4308,42 +4308,42 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C253" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4353,12 +4353,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4368,12 +4368,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4383,12 +4383,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4398,12 +4398,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4413,12 +4413,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4428,12 +4428,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4443,12 +4443,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4458,12 +4458,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4473,12 +4473,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4488,12 +4488,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4503,12 +4503,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4518,12 +4518,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4533,12 +4533,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4548,12 +4548,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4563,12 +4563,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4578,12 +4578,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4593,12 +4593,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4608,12 +4608,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4623,12 +4623,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4638,12 +4638,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4653,12 +4653,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4668,12 +4668,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4683,12 +4683,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4698,12 +4698,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4713,12 +4713,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4728,12 +4728,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4743,12 +4743,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4758,12 +4758,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4773,12 +4773,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4788,12 +4788,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4803,12 +4803,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sh_nbc</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴부천점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4818,12 +4818,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4833,12 +4833,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4848,12 +4848,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4863,12 +4863,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4878,12 +4878,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4893,42 +4893,42 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C292" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4938,12 +4938,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4953,12 +4953,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>dia_inn</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리인</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4968,12 +4968,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4983,12 +4983,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>dia_inn</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>다이아에그 미스테리인</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4998,12 +4998,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5013,12 +5013,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5028,12 +5028,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5043,12 +5043,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5058,12 +5058,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5073,12 +5073,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5088,12 +5088,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5103,12 +5103,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5118,12 +5118,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5133,12 +5133,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5148,12 +5148,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5163,12 +5163,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5178,12 +5178,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5193,12 +5193,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5208,12 +5208,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5223,42 +5223,42 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C314" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5268,12 +5268,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5283,12 +5283,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5298,12 +5298,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ser_dsr</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 대구동성로점</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5313,12 +5313,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5328,12 +5328,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>ser_dsr</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>서울이스케이프룸 대구동성로점</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5343,57 +5343,57 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>sh_sw_2</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>셜록홈즈 수원역2호점 (T.A)</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5403,105 +5403,150 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>otv_dj</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>오렌지티비 대전은행점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>otv_dsr</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>오렌지티비 대구동성로점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>zw_gp</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>제로월드 김포본점</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
+          <t>otv_dj</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>오렌지티비 대전은행점</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>otv_dsr</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>오렌지티비 대구동성로점</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C332" t="n">
+      <c r="C335" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -648,12 +648,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>etp_d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>엔터팟 1호점</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -663,12 +663,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>etp_d</t>
+          <t>ft_str1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엔터팟 1호점</t>
+          <t>판타스트릭 1호점</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -678,12 +678,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ft_str1</t>
+          <t>ft_str2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>판타스트릭 1호점</t>
+          <t>판타스트릭 2호점</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -693,12 +693,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ft_str2</t>
+          <t>lt_ss</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>판타스트릭 2호점</t>
+          <t>레토 성수</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -708,12 +708,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gk_ca</t>
+          <t>mhz_esc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>황금열쇠 천안아케이드점</t>
+          <t>MHZ ESCAPE</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -723,12 +723,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>lt_ss</t>
+          <t>my_dam</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>레토 성수</t>
+          <t>미스터리 담</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -738,12 +738,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>mhz_esc</t>
+          <t>mz_gn</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MHZ ESCAPE</t>
+          <t>괴담저장소 제일기숙학원</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -753,12 +753,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>my_dam</t>
+          <t>mz_hd</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>미스터리 담</t>
+          <t>괴담저장소 한강대 담력훈련</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -768,12 +768,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mz_gn</t>
+          <t>ne_bnr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>괴담저장소 제일기숙학원</t>
+          <t>넥스트에디션 건대 보네르관</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -783,12 +783,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mz_hd</t>
+          <t>pa_hd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>괴담저장소 한강대 담력훈련</t>
+          <t>플레이아레나 홍대점</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -798,12 +798,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ne_bnr</t>
+          <t>plus_esc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대 보네르관</t>
+          <t>플러스 이스케이프</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -813,12 +813,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pa_hd</t>
+          <t>pm_bs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>플레이아레나 홍대점</t>
+          <t>파노라마 부산점</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -828,12 +828,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>plus_esc</t>
+          <t>pm_hd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>플러스 이스케이프</t>
+          <t>파노라마 홍대입구점</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -843,12 +843,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pm_bs</t>
+          <t>pm_hs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>파노라마 부산점</t>
+          <t>파노라마 홍대삼거리점</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -858,12 +858,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pm_hd</t>
+          <t>pm_lw</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파노라마 홍대입구점</t>
+          <t>파노라마X롯데월드</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pm_hs</t>
+          <t>qc_mk</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>파노라마 홍대삼거리점</t>
+          <t>퀘스천마크</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -888,12 +888,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pm_lw</t>
+          <t>rle_sl2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>파노라마X롯데월드</t>
+          <t>룸엘이스케이프 신림2호점</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -903,12 +903,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>qc_mk</t>
+          <t>rle_sl3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>퀘스천마크</t>
+          <t>룸엘이스케이프 신림3호점</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -918,12 +918,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>rle_sl2</t>
+          <t>se_ss</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림2호점</t>
+          <t>싸인이스케이프 상수점</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -933,12 +933,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>rle_sl3</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림3호점</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -948,12 +948,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>se_ss</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>싸인이스케이프 상수점</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -963,12 +963,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -978,42 +978,42 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1023,12 +1023,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1038,12 +1038,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1053,12 +1053,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1068,12 +1068,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>dia_town</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>다이아에그 미스테리타운</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1083,12 +1083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1098,12 +1098,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dia_town</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리타운</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1113,12 +1113,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1128,12 +1128,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1143,12 +1143,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>ft_str3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>판타스트릭 TGC</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1158,12 +1158,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ft_str3</t>
+          <t>gk_ca</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>판타스트릭 TGC</t>
+          <t>황금열쇠 천안아케이드점</t>
         </is>
       </c>
       <c r="C43" t="n">

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,34 +445,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nc_kd</t>
+          <t>csh_gn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>뉴케이스 건대점</t>
+          <t>방탈출 초상화</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>xcp_gn</t>
+          <t>nc_kd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>엑스케이프 강남점</t>
+          <t>뉴케이스 건대점</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>xcp_gn</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>엑스케이프 강남점</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>xcr_kd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>엑스크라임 건대점</t>
         </is>
@@ -520,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C335"/>
+  <dimension ref="A1:C334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,12 +1035,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1038,12 +1050,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1053,12 +1065,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>dia_town</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>다이아에그 미스테리타운</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1068,12 +1080,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dia_town</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리타운</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1083,12 +1095,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1098,12 +1110,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1113,12 +1125,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1128,12 +1140,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>ft_str3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>판타스트릭 TGC</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1143,12 +1155,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ft_str3</t>
+          <t>gk_ca</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>판타스트릭 TGC</t>
+          <t>황금열쇠 천안아케이드점</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1158,12 +1170,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gk_ca</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>황금열쇠 천안아케이드점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1173,12 +1185,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1188,12 +1200,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1203,12 +1215,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1218,12 +1230,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1233,12 +1245,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1248,12 +1260,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1263,12 +1275,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1278,12 +1290,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1293,12 +1305,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1308,12 +1320,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1323,12 +1335,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1338,12 +1350,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1353,12 +1365,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1368,12 +1380,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1383,12 +1395,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1398,12 +1410,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1413,12 +1425,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1428,12 +1440,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1443,12 +1455,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1458,12 +1470,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1473,12 +1485,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1488,27 +1500,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>33_dj</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>33_dj</t>
+          <t>33_kd</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PLAY33 대전점</t>
+          <t>PLAY33 건대점</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1518,12 +1530,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>33_kd</t>
+          <t>bp_ds</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PLAY33 건대점</t>
+          <t>비트포비아 던전스텔라</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1533,12 +1545,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bp_ds</t>
+          <t>bp_sd</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>비트포비아 던전스텔라</t>
+          <t>비트포비아 서면던전</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1548,12 +1560,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>bp_sd</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1563,12 +1575,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ccr_1089</t>
+          <t>cd_ht</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>쿠쿠룸 1089</t>
+          <t>코드헌터 강남점</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1578,12 +1590,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cd_ht</t>
+          <t>cde_grs</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>코드헌터 강남점</t>
+          <t>코드이스케이프 가로수길점</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1593,12 +1605,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cde_grs</t>
+          <t>clv_tw</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>코드이스케이프 가로수길점</t>
+          <t>클레버타운</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1608,12 +1620,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>clv_tw</t>
+          <t>d_coder</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>클레버타운</t>
+          <t>Decoder</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1623,12 +1635,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>d_coder</t>
+          <t>de_bp</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Decoder</t>
+          <t>도어이스케이프 부평점</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1638,12 +1650,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>de_bp</t>
+          <t>de_sr</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>도어이스케이프 부평점</t>
+          <t>도어이스케이프 신논현 레드점</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1653,12 +1665,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>de_sr</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 레드점</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1668,12 +1680,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>dm_fear</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>둠이스케이프 FEAR점</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1683,12 +1695,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dm_fear</t>
+          <t>ect_sc</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>둠이스케이프 FEAR점</t>
+          <t>이스케이프시티 그랜드 시티 신촌점</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1698,12 +1710,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ect_sc</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>이스케이프시티 그랜드 시티 신촌점</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1713,12 +1725,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>epsd_gn</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 강남점</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1728,12 +1740,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1743,12 +1755,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>key_el</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>키이스케이프X에버랜드 메모리카니발</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1758,12 +1770,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>key_el</t>
+          <t>key_gn</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>키이스케이프X에버랜드 메모리카니발</t>
+          <t>키이스케이프 강남점</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1773,12 +1785,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>key_gn</t>
+          <t>key_hd</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>키이스케이프 강남점</t>
+          <t>키이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1788,12 +1800,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>key_hd</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>키이스케이프 홍대점</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1803,12 +1815,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1818,12 +1830,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1833,12 +1845,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1848,12 +1860,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1863,12 +1875,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1878,12 +1890,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1893,12 +1905,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>mp_kd2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>머더파커 건대2호점</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1908,12 +1920,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mp_kd2</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>머더파커 건대2호점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1923,12 +1935,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1938,12 +1950,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1953,12 +1965,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1968,12 +1980,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>pnc_md</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>패닉이스케이프 목동점</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1983,12 +1995,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>pnc_md</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>패닉이스케이프 목동점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1998,12 +2010,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2013,12 +2025,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2028,12 +2040,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2043,12 +2055,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2058,12 +2070,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2073,12 +2085,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2088,12 +2100,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2103,12 +2115,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sg_jj</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>비밀의 화원 전주점</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2118,12 +2130,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2133,12 +2145,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2148,12 +2160,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>sv_kd1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>솔버 1호점</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2163,12 +2175,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sv_kd1</t>
+          <t>sv_kd2</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>솔버 1호점</t>
+          <t>솔버 2호점</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2178,12 +2190,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>sv_kd2</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>솔버 2호점</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2193,12 +2205,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2208,27 +2220,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2238,12 +2250,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2253,12 +2265,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2268,12 +2280,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2283,12 +2295,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2298,12 +2310,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2313,12 +2325,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2328,12 +2340,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2343,12 +2355,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2358,12 +2370,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2373,12 +2385,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2388,12 +2400,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2403,12 +2415,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2418,12 +2430,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>ect_bc</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>이스케이프시티 부천신중동점</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2433,12 +2445,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ect_bc</t>
+          <t>ep_lg</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>이스케이프시티 부천신중동점</t>
+          <t>에필로그</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2448,12 +2460,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ep_lg</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>에필로그</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2463,12 +2475,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>gom_sm</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>게임 오브 마인드 서면점</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2478,12 +2490,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>gom_sm</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>게임 오브 마인드 서면점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2493,12 +2505,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2508,12 +2520,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2523,12 +2535,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2538,12 +2550,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2553,12 +2565,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2568,12 +2580,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2583,12 +2595,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2598,12 +2610,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>머더파커 전주2호점 어드벤처</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2613,12 +2625,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점 어드벤처</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2628,12 +2640,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2643,12 +2655,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2658,12 +2670,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2673,12 +2685,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2688,12 +2700,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2703,12 +2715,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2718,12 +2730,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2733,12 +2745,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2748,12 +2760,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2763,12 +2775,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2778,12 +2790,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2793,12 +2805,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2808,12 +2820,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2823,12 +2835,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2838,12 +2850,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2853,12 +2865,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2868,12 +2880,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2883,12 +2895,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2898,12 +2910,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2913,12 +2925,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2928,12 +2940,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2943,12 +2955,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2958,12 +2970,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2973,12 +2985,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2988,12 +3000,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3003,12 +3015,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3018,12 +3030,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3033,12 +3045,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3048,12 +3060,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3063,12 +3075,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3078,12 +3090,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3093,12 +3105,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3108,12 +3120,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3123,12 +3135,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sw_lab</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>수원방탈출연구소</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3138,12 +3150,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>sw_lab</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>수원방탈출연구소</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3153,12 +3165,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3168,12 +3180,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3183,12 +3195,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3198,12 +3210,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3213,12 +3225,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3228,27 +3240,27 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3258,12 +3270,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3273,12 +3285,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3288,12 +3300,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3303,12 +3315,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>crew_sc2</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>탐정크루 신촌2호점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3318,12 +3330,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3333,12 +3345,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3348,12 +3360,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3363,12 +3375,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3378,12 +3390,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3393,12 +3405,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ect_sswu</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>이스케이프시티 성신여대점</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3408,12 +3420,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3423,12 +3435,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3438,12 +3450,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>find_esc</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>더파인더 방탈출</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3453,12 +3465,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3468,12 +3480,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3483,12 +3495,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3498,12 +3510,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3513,12 +3525,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3528,12 +3540,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3543,12 +3555,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3558,12 +3570,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3573,12 +3585,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3588,12 +3600,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3603,12 +3615,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>머더파커 전주3호점 E.T</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3618,12 +3630,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점 E.T</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3633,12 +3645,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3648,12 +3660,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3663,12 +3675,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3678,12 +3690,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3693,12 +3705,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3708,12 +3720,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3723,12 +3735,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3738,12 +3750,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3753,12 +3765,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3768,12 +3780,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3783,12 +3795,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3798,12 +3810,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3813,12 +3825,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3828,12 +3840,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3843,12 +3855,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3858,12 +3870,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3873,12 +3885,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3888,12 +3900,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ser_bp</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부평점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3903,12 +3915,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ser_sm</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부산서면점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3918,12 +3930,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3933,12 +3945,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3948,12 +3960,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3963,12 +3975,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3978,12 +3990,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3993,12 +4005,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4008,12 +4020,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4023,12 +4035,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4038,12 +4050,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4053,12 +4065,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4068,12 +4080,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4083,12 +4095,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4098,12 +4110,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4113,12 +4125,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4128,12 +4140,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4143,12 +4155,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4158,12 +4170,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4173,12 +4185,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4188,12 +4200,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4203,12 +4215,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_yb</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 용인역북점 (T.A)</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4218,12 +4230,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>sh_yb</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인역북점 (T.A)</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4233,12 +4245,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4248,12 +4260,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4263,12 +4275,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4278,12 +4290,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4293,12 +4305,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4308,12 +4320,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4323,27 +4335,27 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4353,12 +4365,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4368,12 +4380,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4383,12 +4395,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4398,12 +4410,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4413,12 +4425,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4428,12 +4440,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4443,12 +4455,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4458,12 +4470,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4473,12 +4485,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4488,12 +4500,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4503,12 +4515,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4518,12 +4530,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4533,12 +4545,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4548,12 +4560,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4563,12 +4575,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4578,12 +4590,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4593,12 +4605,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4608,12 +4620,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4623,12 +4635,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4638,12 +4650,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4653,12 +4665,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4668,12 +4680,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4683,12 +4695,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4698,12 +4710,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4713,12 +4725,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4728,12 +4740,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4743,12 +4755,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4758,12 +4770,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4773,12 +4785,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4788,12 +4800,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4803,12 +4815,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4818,12 +4830,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4833,12 +4845,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>sh_nbc</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴부천점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4848,12 +4860,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4863,12 +4875,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4878,12 +4890,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4893,12 +4905,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4908,27 +4920,27 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4938,12 +4950,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4953,12 +4965,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4968,12 +4980,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>dia_inn</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>다이아에그 미스테리인</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4983,12 +4995,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>dia_inn</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리인</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4998,12 +5010,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5013,12 +5025,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5028,12 +5040,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5043,12 +5055,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5058,12 +5070,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5073,12 +5085,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5088,12 +5100,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5103,12 +5115,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5118,12 +5130,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5133,12 +5145,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5148,12 +5160,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5163,12 +5175,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5178,12 +5190,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5193,12 +5205,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5208,12 +5220,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5223,12 +5235,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5238,27 +5250,27 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5268,12 +5280,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5283,12 +5295,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5298,12 +5310,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5313,12 +5325,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>ser_dsr</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>서울이스케이프룸 대구동성로점</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5328,12 +5340,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ser_dsr</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 대구동성로점</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5343,12 +5355,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>sh_sw_2</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>셜록홈즈 수원역2호점 (T.A)</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5358,12 +5370,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>sh_sw_2</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역2호점 (T.A)</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5373,27 +5385,27 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5403,12 +5415,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5418,27 +5430,27 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -5448,27 +5460,27 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>zw_gp</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>제로월드 김포본점</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5478,27 +5490,27 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>otv_dj</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>오렌지티비 대전은행점</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>otv_dj</t>
+          <t>otv_dsr</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>오렌지티비 대전은행점</t>
+          <t>오렌지티비 대구동성로점</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5508,45 +5520,30 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>otv_dsr</t>
+          <t>ck_gn</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>오렌지티비 대구동성로점</t>
+          <t>코드케이 강남점</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>tte_hd</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>티켓투이스케이프</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>tte_hd</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>티켓투이스케이프</t>
-        </is>
-      </c>
-      <c r="C335" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,46 +445,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>csh_gn</t>
+          <t>nc_kd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>방탈출 초상화</t>
+          <t>뉴케이스 건대점</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>nc_kd</t>
+          <t>xcp_gn</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>뉴케이스 건대점</t>
+          <t>엑스케이프 강남점</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>xcp_gn</t>
+          <t>xcr_kd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
-        <is>
-          <t>엑스케이프 강남점</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>xcr_kd</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
         <is>
           <t>엑스크라임 건대점</t>
         </is>
@@ -532,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C334"/>
+  <dimension ref="A1:C335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,27 +978,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>zw_kd</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>제로월드 다이브 건대점</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1020,12 +1008,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1035,12 +1023,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1050,12 +1038,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1065,12 +1053,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dia_town</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리타운</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1080,12 +1068,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>dia_town</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>다이아에그 미스테리타운</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1095,12 +1083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1110,12 +1098,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1125,12 +1113,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1140,12 +1128,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ft_str3</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>판타스트릭 TGC</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1155,12 +1143,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>gk_ca</t>
+          <t>ft_str3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>황금열쇠 천안아케이드점</t>
+          <t>판타스트릭 TGC</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1170,12 +1158,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>gk_ca</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>황금열쇠 천안아케이드점</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1185,12 +1173,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1200,12 +1188,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1215,12 +1203,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1230,12 +1218,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1245,12 +1233,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1260,12 +1248,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1275,12 +1263,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1290,12 +1278,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1305,12 +1293,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1320,12 +1308,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1335,12 +1323,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1350,12 +1338,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1365,12 +1353,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1380,12 +1368,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1395,12 +1383,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1410,12 +1398,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1425,12 +1413,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1440,12 +1428,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1455,12 +1443,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1470,12 +1458,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1485,12 +1473,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1500,27 +1488,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>33_dj</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PLAY33 대전점</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>33_kd</t>
+          <t>33_dj</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PLAY33 건대점</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1530,12 +1518,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>bp_ds</t>
+          <t>33_kd</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>비트포비아 던전스텔라</t>
+          <t>PLAY33 건대점</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1545,12 +1533,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bp_sd</t>
+          <t>bp_ds</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전</t>
+          <t>비트포비아 던전스텔라</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1560,12 +1548,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ccr_1089</t>
+          <t>bp_sd</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>쿠쿠룸 1089</t>
+          <t>비트포비아 서면던전</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1575,12 +1563,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cd_ht</t>
+          <t>ccr_1089</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>코드헌터 강남점</t>
+          <t>쿠쿠룸 1089</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1590,12 +1578,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cde_grs</t>
+          <t>cd_ht</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>코드이스케이프 가로수길점</t>
+          <t>코드헌터 강남점</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1605,12 +1593,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>clv_tw</t>
+          <t>cde_grs</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>클레버타운</t>
+          <t>코드이스케이프 가로수길점</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1620,12 +1608,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>d_coder</t>
+          <t>clv_tw</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Decoder</t>
+          <t>클레버타운</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -1635,12 +1623,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>de_bp</t>
+          <t>d_coder</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>도어이스케이프 부평점</t>
+          <t>Decoder</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1650,12 +1638,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>de_sr</t>
+          <t>de_bp</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 레드점</t>
+          <t>도어이스케이프 부평점</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1665,12 +1653,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>de_sr</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>도어이스케이프 신논현 레드점</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1680,12 +1668,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>dm_fear</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>둠이스케이프 FEAR점</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1695,12 +1683,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ect_sc</t>
+          <t>dm_fear</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>이스케이프시티 그랜드 시티 신촌점</t>
+          <t>둠이스케이프 FEAR점</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1710,12 +1698,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>epsd_gn</t>
+          <t>ect_sc</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 강남점</t>
+          <t>이스케이프시티 그랜드 시티 신촌점</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1725,12 +1713,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1740,12 +1728,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1755,12 +1743,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>key_el</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>키이스케이프X에버랜드 메모리카니발</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1770,12 +1758,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>key_gn</t>
+          <t>key_el</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>키이스케이프 강남점</t>
+          <t>키이스케이프X에버랜드 메모리카니발</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1785,12 +1773,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>key_hd</t>
+          <t>key_gn</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>키이스케이프 홍대점</t>
+          <t>키이스케이프 강남점</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1800,12 +1788,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>key_hd</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>키이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1815,12 +1803,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1830,12 +1818,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1845,12 +1833,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1860,12 +1848,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1875,12 +1863,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1890,12 +1878,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1905,12 +1893,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mp_kd2</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>머더파커 건대2호점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1920,12 +1908,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>mp_kd2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>머더파커 건대2호점</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1935,12 +1923,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1950,12 +1938,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1965,12 +1953,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1980,12 +1968,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>pnc_md</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>패닉이스케이프 목동점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1995,12 +1983,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>pnc_md</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>패닉이스케이프 목동점</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2010,12 +1998,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2025,12 +2013,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2040,12 +2028,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2055,12 +2043,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2070,12 +2058,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2085,12 +2073,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2100,12 +2088,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>sg_jj</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>비밀의 화원 전주점</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2115,12 +2103,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2130,12 +2118,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2145,12 +2133,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2160,12 +2148,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sv_kd1</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>솔버 1호점</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2175,12 +2163,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sv_kd2</t>
+          <t>sv_kd1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>솔버 2호점</t>
+          <t>솔버 1호점</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2190,12 +2178,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>sv_kd2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>솔버 2호점</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2205,12 +2193,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2220,27 +2208,27 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -2250,12 +2238,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2265,12 +2253,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2280,12 +2268,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2295,12 +2283,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2310,12 +2298,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2325,12 +2313,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2340,12 +2328,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2355,12 +2343,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2370,12 +2358,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2385,12 +2373,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2400,12 +2388,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2415,12 +2403,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2430,12 +2418,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ect_bc</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>이스케이프시티 부천신중동점</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2445,12 +2433,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ep_lg</t>
+          <t>ect_bc</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>에필로그</t>
+          <t>이스케이프시티 부천신중동점</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2460,12 +2448,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>ep_lg</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>에필로그</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2475,12 +2463,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>gom_sm</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>게임 오브 마인드 서면점</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2490,12 +2478,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>gom_sm</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>게임 오브 마인드 서면점</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2505,12 +2493,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2520,12 +2508,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2535,12 +2523,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2550,12 +2538,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2565,12 +2553,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2580,12 +2568,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2595,12 +2583,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2610,12 +2598,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점 어드벤처</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2625,12 +2613,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>머더파커 전주2호점 어드벤처</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2640,12 +2628,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2655,12 +2643,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2670,12 +2658,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2685,12 +2673,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2700,12 +2688,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2715,12 +2703,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2730,12 +2718,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2745,12 +2733,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2760,12 +2748,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2775,12 +2763,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2790,12 +2778,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2805,12 +2793,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2820,12 +2808,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2835,12 +2823,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2850,12 +2838,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2865,12 +2853,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2880,12 +2868,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2895,12 +2883,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2910,12 +2898,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2925,12 +2913,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2940,12 +2928,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2955,12 +2943,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2970,12 +2958,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2985,12 +2973,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3000,12 +2988,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3015,12 +3003,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3030,12 +3018,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3045,12 +3033,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3060,12 +3048,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3075,12 +3063,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3090,12 +3078,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3105,12 +3093,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3120,12 +3108,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3135,12 +3123,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>sw_lab</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>수원방탈출연구소</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3150,12 +3138,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>sw_lab</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>수원방탈출연구소</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3165,12 +3153,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3180,12 +3168,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3195,12 +3183,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3210,12 +3198,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3225,12 +3213,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3240,27 +3228,27 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3270,12 +3258,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3285,12 +3273,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3300,12 +3288,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>crew_sc2</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>탐정크루 신촌2호점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3315,12 +3303,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3330,12 +3318,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3345,12 +3333,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3360,12 +3348,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3375,12 +3363,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3390,12 +3378,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ect_sswu</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>이스케이프시티 성신여대점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3405,12 +3393,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3420,12 +3408,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3435,12 +3423,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>find_esc</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>더파인더 방탈출</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3450,12 +3438,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3465,12 +3453,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3480,12 +3468,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3495,12 +3483,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3510,12 +3498,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3525,12 +3513,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3540,12 +3528,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3555,12 +3543,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3570,12 +3558,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3585,12 +3573,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3600,12 +3588,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3615,12 +3603,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점 E.T</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3630,12 +3618,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>머더파커 전주3호점 E.T</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3645,12 +3633,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3660,12 +3648,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3675,12 +3663,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3690,12 +3678,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3705,12 +3693,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3720,12 +3708,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3735,12 +3723,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3750,12 +3738,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3765,12 +3753,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3780,12 +3768,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3795,12 +3783,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3810,12 +3798,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3825,12 +3813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3840,12 +3828,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3855,12 +3843,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3870,12 +3858,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3885,12 +3873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ser_bp</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부평점</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3900,12 +3888,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ser_sm</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부산서면점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3915,12 +3903,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3930,12 +3918,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3945,12 +3933,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3960,12 +3948,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3975,12 +3963,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3990,12 +3978,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4005,12 +3993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4020,12 +4008,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4035,12 +4023,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4050,12 +4038,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4065,12 +4053,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4080,12 +4068,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4095,12 +4083,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4110,12 +4098,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4125,12 +4113,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4140,12 +4128,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4155,12 +4143,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4170,12 +4158,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4185,12 +4173,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4200,12 +4188,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4215,12 +4203,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>sh_yb</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인역북점 (T.A)</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4230,12 +4218,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sh_yb</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>셜록홈즈 용인역북점 (T.A)</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4245,12 +4233,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4260,12 +4248,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4275,12 +4263,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4290,12 +4278,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4305,12 +4293,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4320,12 +4308,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4335,27 +4323,27 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C254" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -4365,12 +4353,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4380,12 +4368,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4395,12 +4383,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4410,12 +4398,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4425,12 +4413,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4440,12 +4428,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4455,12 +4443,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4470,12 +4458,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4485,12 +4473,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4500,12 +4488,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4515,12 +4503,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4530,12 +4518,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4545,12 +4533,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4560,12 +4548,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4575,12 +4563,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4590,12 +4578,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4605,12 +4593,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4620,12 +4608,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4635,12 +4623,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4650,12 +4638,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4665,12 +4653,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4680,12 +4668,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4695,12 +4683,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4710,12 +4698,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4725,12 +4713,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4740,12 +4728,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4755,12 +4743,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4770,12 +4758,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4785,12 +4773,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4800,12 +4788,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4815,12 +4803,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4830,12 +4818,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>sh_nbc</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴부천점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4845,12 +4833,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4860,12 +4848,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4875,12 +4863,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4890,12 +4878,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4905,12 +4893,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4920,27 +4908,27 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C293" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4950,12 +4938,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4965,12 +4953,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4980,12 +4968,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>dia_inn</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리인</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4995,12 +4983,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>dia_inn</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>다이아에그 미스테리인</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -5010,12 +4998,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5025,12 +5013,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5040,12 +5028,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5055,12 +5043,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5070,12 +5058,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5085,12 +5073,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5100,12 +5088,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5115,12 +5103,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5130,12 +5118,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5145,12 +5133,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5160,12 +5148,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5175,12 +5163,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5190,12 +5178,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5205,12 +5193,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5220,12 +5208,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5235,12 +5223,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5250,27 +5238,27 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C315" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5280,12 +5268,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5295,12 +5283,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5310,12 +5298,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5325,12 +5313,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ser_dsr</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 대구동성로점</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5340,12 +5328,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>ser_dsr</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>서울이스케이프룸 대구동성로점</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5355,12 +5343,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>sh_sw_2</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역2호점 (T.A)</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5370,12 +5358,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>sh_sw_2</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>셜록홈즈 수원역2호점 (T.A)</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5385,27 +5373,27 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5415,12 +5403,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5430,27 +5418,27 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -5460,27 +5448,27 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5490,27 +5478,27 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>otv_dj</t>
+          <t>zw_gp</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>오렌지티비 대전은행점</t>
+          <t>제로월드 김포본점</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>otv_dsr</t>
+          <t>otv_dj</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>오렌지티비 대구동성로점</t>
+          <t>오렌지티비 대전은행점</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5520,30 +5508,45 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>otv_dsr</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>오렌지티비 대구동성로점</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C334" t="n">
+      <c r="C335" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C335"/>
+  <dimension ref="A1:C336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2688,12 +2688,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ne_bc</t>
+          <t>mz_kd</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>넥스트에디션 부천점</t>
+          <t>더메이즈 건대점</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2703,12 +2703,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ne_js</t>
+          <t>ne_bc</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>넥스트에디션 잠실점</t>
+          <t>넥스트에디션 부천점</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -2718,12 +2718,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>osm_hd</t>
+          <t>ne_js</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>오아시스 뮤지엄</t>
+          <t>넥스트에디션 잠실점</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2733,12 +2733,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>pn_gn</t>
+          <t>osm_hd</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>포인트나인 강남점</t>
+          <t>오아시스 뮤지엄</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -2748,12 +2748,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ppl_bso</t>
+          <t>pn_gn</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>플레이포인트랩 부산서면오리진점</t>
+          <t>포인트나인 강남점</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2763,12 +2763,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ppl_nw</t>
+          <t>ppl_bso</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>플레이포인트랩 노원점</t>
+          <t>플레이포인트랩 부산서면오리진점</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2778,12 +2778,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ptw_dsr</t>
+          <t>ppl_nw</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>플레이더월드 동성로점</t>
+          <t>플레이포인트랩 노원점</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -2793,12 +2793,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ra_bp</t>
+          <t>ptw_dsr</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>룸즈에이 부평점</t>
+          <t>플레이더월드 동성로점</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -2808,12 +2808,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ra_bp2</t>
+          <t>ra_bp</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>룸즈에이 부평2호점</t>
+          <t>룸즈에이 부평점</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -2823,12 +2823,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ra_eh</t>
+          <t>ra_bp2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>룸즈에이 대전은행점</t>
+          <t>룸즈에이 부평2호점</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2838,12 +2838,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ra_gsw2</t>
+          <t>ra_eh</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완2호점</t>
+          <t>룸즈에이 대전은행점</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2853,12 +2853,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ra_lf</t>
+          <t>ra_gsw2</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 라페스타점</t>
+          <t>룸즈에이 광주수완2호점</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -2868,12 +2868,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ra_ph</t>
+          <t>ra_lf</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>룸즈에이 포항점</t>
+          <t>룸즈에이 일산 라페스타점</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2883,12 +2883,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ra_sw</t>
+          <t>ra_ph</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역점</t>
+          <t>룸즈에이 포항점</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2898,12 +2898,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ra_sw2</t>
+          <t>ra_sw</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>룸즈에이 수원역2호점</t>
+          <t>룸즈에이 수원역점</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2913,12 +2913,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>rex_bk</t>
+          <t>ra_sw2</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>룸익스케이프 BLACK</t>
+          <t>룸즈에이 수원역2호점</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -2928,12 +2928,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rh_rm</t>
+          <t>rex_bk</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>러시아워 2호점 로드맨션</t>
+          <t>룸익스케이프 BLACK</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -2943,12 +2943,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>rle_sl1</t>
+          <t>rh_rm</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림점</t>
+          <t>러시아워 2호점 로드맨션</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -2958,12 +2958,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>sg_fkd</t>
+          <t>rle_sl1</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>비밀의 화원 포레스트건대점</t>
+          <t>룸엘이스케이프 신림점</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -2973,12 +2973,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sg_hj</t>
+          <t>sg_fkd</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>비밀의 화원 미드나잇 합정점</t>
+          <t>비밀의 화원 포레스트건대점</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -2988,12 +2988,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>sgn_grs</t>
+          <t>sg_hj</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>시그널헌터 가로수길점</t>
+          <t>비밀의 화원 미드나잇 합정점</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3003,12 +3003,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>sh_bc</t>
+          <t>sgn_grs</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>셜록홈즈 부천중동점 (T.A)</t>
+          <t>시그널헌터 가로수길점</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3018,12 +3018,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>sh_ca2</t>
+          <t>sh_bc</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안2호점</t>
+          <t>셜록홈즈 부천중동점 (T.A)</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -3033,12 +3033,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>sh_dsr</t>
+          <t>sh_ca2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>셜록홈즈 대구동성로점</t>
+          <t>셜록홈즈 천안2호점</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -3048,12 +3048,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>sh_ms</t>
+          <t>sh_dsr</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>셜록홈즈 미사점 (T.A)</t>
+          <t>셜록홈즈 대구동성로점</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3063,12 +3063,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>sh_nrj</t>
+          <t>sh_ms</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>셜록홈즈 노량진점</t>
+          <t>셜록홈즈 미사점 (T.A)</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3078,12 +3078,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>sh_sh</t>
+          <t>sh_nrj</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>셜록홈즈 서현점</t>
+          <t>셜록홈즈 노량진점</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3093,12 +3093,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>sh_sswu</t>
+          <t>sh_sh</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>셜록홈즈 성신여대점</t>
+          <t>셜록홈즈 서현점</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3108,12 +3108,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>sm_bp</t>
+          <t>sh_sswu</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>상상의 문 부평점</t>
+          <t>셜록홈즈 성신여대점</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3123,12 +3123,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>sr_hd</t>
+          <t>sm_bp</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>쇼룸 404</t>
+          <t>상상의 문 부평점</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3138,12 +3138,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>sw_lab</t>
+          <t>sr_hd</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>수원방탈출연구소</t>
+          <t>쇼룸 404</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3153,12 +3153,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>tcd_cc</t>
+          <t>sw_lab</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>더 코드 춘천점</t>
+          <t>수원방탈출연구소</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3168,12 +3168,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>tcd_gj</t>
+          <t>tcd_cc</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>더 코드 경주점</t>
+          <t>더 코드 춘천점</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3183,12 +3183,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>tcd_hg</t>
+          <t>tcd_gj</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>더 코드 회기점</t>
+          <t>더 코드 경주점</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -3198,12 +3198,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>tcd_wsn</t>
+          <t>tcd_hg</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>더 코드 왕십리점</t>
+          <t>더 코드 회기점</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3213,12 +3213,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ts_cag</t>
+          <t>tcd_wsn</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>테라스페이스 아트갤러리점</t>
+          <t>더 코드 왕십리점</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3228,12 +3228,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>xcp_kd</t>
+          <t>ts_cag</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>엑스케이프 건대점</t>
+          <t>테라스페이스 아트갤러리점</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3243,27 +3243,27 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>xcp_kd</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>엑스케이프 건대점</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3273,12 +3273,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3288,12 +3288,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3303,12 +3303,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>crew_sc2</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>탐정크루 신촌2호점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3318,12 +3318,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3333,12 +3333,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3348,12 +3348,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3363,12 +3363,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3378,12 +3378,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3393,12 +3393,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ect_sswu</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>이스케이프시티 성신여대점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3408,12 +3408,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3423,12 +3423,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3438,12 +3438,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>find_esc</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>더파인더 방탈출</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3453,12 +3453,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3468,12 +3468,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3483,12 +3483,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3498,12 +3498,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3513,12 +3513,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3528,12 +3528,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3543,12 +3543,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3558,12 +3558,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3573,12 +3573,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3588,12 +3588,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3603,12 +3603,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3618,12 +3618,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점 E.T</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3633,12 +3633,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>머더파커 전주3호점 E.T</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3648,12 +3648,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3663,12 +3663,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3678,12 +3678,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3693,12 +3693,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3708,12 +3708,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3723,12 +3723,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3738,12 +3738,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3753,12 +3753,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3768,12 +3768,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3783,12 +3783,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3798,12 +3798,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3813,12 +3813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3828,12 +3828,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3843,12 +3843,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3858,12 +3858,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3873,12 +3873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3888,12 +3888,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ser_bp</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부평점</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3903,12 +3903,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ser_sm</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부산서면점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3918,12 +3918,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3933,12 +3933,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3948,12 +3948,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3963,12 +3963,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3978,12 +3978,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3993,12 +3993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4008,12 +4008,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4023,12 +4023,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4038,12 +4038,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4053,12 +4053,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4068,12 +4068,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4083,12 +4083,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4098,12 +4098,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4113,12 +4113,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4128,12 +4128,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4143,12 +4143,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4158,12 +4158,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4173,12 +4173,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4188,12 +4188,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4203,12 +4203,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4218,12 +4218,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>sh_yb</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인역북점 (T.A)</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4233,12 +4233,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sh_yb</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>셜록홈즈 용인역북점 (T.A)</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4248,12 +4248,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4263,12 +4263,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4278,12 +4278,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4293,12 +4293,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4308,12 +4308,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>wtw_esc</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>월투월방탈출 서울대입구점</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4323,12 +4323,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4338,27 +4338,27 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4368,12 +4368,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4383,12 +4383,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4398,12 +4398,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4413,12 +4413,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4428,12 +4428,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4443,12 +4443,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4458,12 +4458,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4473,12 +4473,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4488,12 +4488,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4503,12 +4503,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4518,12 +4518,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4533,12 +4533,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4548,12 +4548,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4563,12 +4563,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4578,12 +4578,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4593,12 +4593,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4608,12 +4608,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4623,12 +4623,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4638,12 +4638,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4653,12 +4653,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4668,12 +4668,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4683,12 +4683,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4698,12 +4698,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4713,12 +4713,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4728,12 +4728,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4743,12 +4743,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4758,12 +4758,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4773,12 +4773,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4788,12 +4788,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4803,12 +4803,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4818,12 +4818,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4833,12 +4833,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>sh_nbc</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴부천점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4848,12 +4848,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4863,12 +4863,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4878,12 +4878,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4893,12 +4893,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4908,12 +4908,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4923,27 +4923,27 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4953,12 +4953,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4968,12 +4968,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4983,12 +4983,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>dia_inn</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리인</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4998,12 +4998,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>dia_inn</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>다이아에그 미스테리인</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5013,12 +5013,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5028,12 +5028,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5043,12 +5043,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5058,12 +5058,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5073,12 +5073,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5088,12 +5088,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5103,12 +5103,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5118,12 +5118,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5133,12 +5133,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5148,12 +5148,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5163,12 +5163,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5178,12 +5178,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5193,12 +5193,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5208,12 +5208,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5223,12 +5223,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5238,12 +5238,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5253,27 +5253,27 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5283,12 +5283,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5298,12 +5298,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5313,12 +5313,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5328,12 +5328,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ser_dsr</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 대구동성로점</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5343,12 +5343,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>ser_dsr</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>서울이스케이프룸 대구동성로점</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5358,12 +5358,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>sh_sw_2</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역2호점 (T.A)</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5373,12 +5373,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>sh_sw_2</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>셜록홈즈 수원역2호점 (T.A)</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -5388,27 +5388,27 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5418,12 +5418,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -5433,27 +5433,27 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -5463,27 +5463,27 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -5493,27 +5493,27 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>otv_dj</t>
+          <t>zw_gp</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>오렌지티비 대전은행점</t>
+          <t>제로월드 김포본점</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>otv_dsr</t>
+          <t>otv_dj</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>오렌지티비 대구동성로점</t>
+          <t>오렌지티비 대전은행점</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -5523,30 +5523,45 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>otv_dsr</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>오렌지티비 대구동성로점</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C335" t="n">
+      <c r="C336" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C336"/>
+  <dimension ref="A1:C337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -768,12 +768,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ne_bnr</t>
+          <t>nbj_ay3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대 보네르관</t>
+          <t>나비잠 3호점</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -783,12 +783,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pa_hd</t>
+          <t>ne_bnr</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>플레이아레나 홍대점</t>
+          <t>넥스트에디션 건대 보네르관</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -798,12 +798,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>plus_esc</t>
+          <t>pa_hd</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>플러스 이스케이프</t>
+          <t>플레이아레나 홍대점</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -813,12 +813,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pm_bs</t>
+          <t>plus_esc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>파노라마 부산점</t>
+          <t>플러스 이스케이프</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -828,12 +828,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pm_hd</t>
+          <t>pm_bs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>파노라마 홍대입구점</t>
+          <t>파노라마 부산점</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -843,12 +843,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pm_hs</t>
+          <t>pm_hd</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>파노라마 홍대삼거리점</t>
+          <t>파노라마 홍대입구점</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -858,12 +858,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pm_lw</t>
+          <t>pm_hs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파노라마X롯데월드</t>
+          <t>파노라마 홍대삼거리점</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>qc_mk</t>
+          <t>pm_lw</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>퀘스천마크</t>
+          <t>파노라마X롯데월드</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -888,12 +888,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rle_sl2</t>
+          <t>qc_mk</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림2호점</t>
+          <t>퀘스천마크</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -903,12 +903,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>rle_sl3</t>
+          <t>rle_sl2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 신림3호점</t>
+          <t>룸엘이스케이프 신림2호점</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -918,12 +918,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>se_ss</t>
+          <t>rle_sl3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>싸인이스케이프 상수점</t>
+          <t>룸엘이스케이프 신림3호점</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -933,12 +933,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ser_hd</t>
+          <t>se_ss</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 홍대점</t>
+          <t>싸인이스케이프 상수점</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -948,12 +948,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>str_mk</t>
+          <t>ser_hd</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>스토리메이커스</t>
+          <t>서울이스케이프룸 홍대점</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -963,12 +963,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>str_mk</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>스토리메이커스</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -978,12 +978,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>zw_kd</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>제로월드 다이브 건대점</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -993,27 +993,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>zw_kd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>제로월드 다이브 건대점</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1023,12 +1023,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1038,12 +1038,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1053,12 +1053,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1068,12 +1068,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dia_town</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리타운</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1083,12 +1083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>dia_town</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>다이아에그 미스테리타운</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1098,12 +1098,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1113,12 +1113,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1128,12 +1128,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1143,12 +1143,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ft_str3</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>판타스트릭 TGC</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1158,12 +1158,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>gk_ca</t>
+          <t>ft_str3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>황금열쇠 천안아케이드점</t>
+          <t>판타스트릭 TGC</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1173,12 +1173,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>gk_ca</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>황금열쇠 천안아케이드점</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1188,12 +1188,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1203,12 +1203,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1218,12 +1218,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1233,12 +1233,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1248,12 +1248,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1263,12 +1263,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1278,12 +1278,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>key_log2</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN2</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1668,12 +1668,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>dle_gn</t>
+          <t>dm_fear</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>돌로이스케이프</t>
+          <t>둠이스케이프 FEAR점</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -1683,12 +1683,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>dm_fear</t>
+          <t>ect_sc</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>둠이스케이프 FEAR점</t>
+          <t>이스케이프시티 그랜드 시티 신촌점</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1698,12 +1698,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ect_sc</t>
+          <t>epsd_gn</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>이스케이프시티 그랜드 시티 신촌점</t>
+          <t>에피소드 방탈출 강남점</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -1713,12 +1713,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>epsd_gn</t>
+          <t>frk_as</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 강남점</t>
+          <t>프랭크의 골동품가게</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1728,12 +1728,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>frk_as</t>
+          <t>ft_sia</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>프랭크의 골동품가게</t>
+          <t>판타지아</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1743,12 +1743,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ft_sia</t>
+          <t>he_gj2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>판타지아</t>
+          <t>숨바꼭질 2호점</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -1803,12 +1803,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>key_mc</t>
+          <t>key_log2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>키이스케이프 메모리컴퍼니</t>
+          <t>키이스케이프 LOG_IN2</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1818,12 +1818,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>key_st</t>
+          <t>key_mc</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>키이스케이프 STATION</t>
+          <t>키이스케이프 메모리컴퍼니</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1833,12 +1833,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>key_wt</t>
+          <t>key_st</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>키이스케이프 후즈데어</t>
+          <t>키이스케이프 STATION</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1848,12 +1848,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>lds_hd</t>
+          <t>key_wt</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>레다스퀘어 홍대점</t>
+          <t>키이스케이프 후즈데어</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -1863,12 +1863,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>mk_kd</t>
+          <t>lds_hd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>마스터키 건대점</t>
+          <t>레다스퀘어 홍대점</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1878,12 +1878,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mp_jj1</t>
+          <t>mk_kd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>머더파커 전주1호점</t>
+          <t>마스터키 건대점</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1893,12 +1893,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>mp_js</t>
+          <t>mp_jj1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>머더파커 잠실점</t>
+          <t>머더파커 전주1호점</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -1908,12 +1908,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>mp_kd2</t>
+          <t>mp_js</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>머더파커 건대2호점</t>
+          <t>머더파커 잠실점</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1923,12 +1923,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>mpw_hd</t>
+          <t>mp_kd2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>머더파커 WOW 홍대점</t>
+          <t>머더파커 건대2호점</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1938,12 +1938,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>nbj_ay1</t>
+          <t>mpw_hd</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>나비잠 1호점</t>
+          <t>머더파커 WOW 홍대점</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1953,12 +1953,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>nbj_ay2</t>
+          <t>nbj_ay1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>나비잠 2호점</t>
+          <t>나비잠 1호점</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1968,12 +1968,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>pn_kd</t>
+          <t>nbj_ay2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>포인트나인 건대점</t>
+          <t>나비잠 2호점</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1983,12 +1983,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>pnc_md</t>
+          <t>pn_kd</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>패닉이스케이프 목동점</t>
+          <t>포인트나인 건대점</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1998,12 +1998,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ppl_hd</t>
+          <t>pnc_md</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>플레이포인트랩 홍대점</t>
+          <t>패닉이스케이프 목동점</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2013,12 +2013,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ppl_sts</t>
+          <t>ppl_hd</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>플레이포인트랩 서면탄탄스트리트점</t>
+          <t>플레이포인트랩 홍대점</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -2028,12 +2028,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ra_ay</t>
+          <t>ppl_sts</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>룸즈에이 안양범계점</t>
+          <t>플레이포인트랩 서면탄탄스트리트점</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2043,12 +2043,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>rex_ib</t>
+          <t>ra_ay</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>룸익스케이프 INDIGO BLUE</t>
+          <t>룸즈에이 안양범계점</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2058,12 +2058,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>sc_ppl</t>
+          <t>rex_ib</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>신촌퍼플릭</t>
+          <t>룸익스케이프 INDIGO BLUE</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2073,12 +2073,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>se_gn</t>
+          <t>sc_ppl</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>싸인이스케이프 강남시티점</t>
+          <t>신촌퍼플릭</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2088,12 +2088,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>se_hd</t>
+          <t>se_gn</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>싸인이스케이프 홍대점</t>
+          <t>싸인이스케이프 강남시티점</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2103,12 +2103,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>sg_jj</t>
+          <t>se_hd</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>비밀의 화원 전주점</t>
+          <t>싸인이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2118,12 +2118,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>sh_dj</t>
+          <t>sg_jj</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>셜록홈즈 대전은행점 (T.A)</t>
+          <t>비밀의 화원 전주점</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2133,12 +2133,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>sh_jssn</t>
+          <t>sh_dj</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실새내점 (T.A)</t>
+          <t>셜록홈즈 대전은행점 (T.A)</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2148,12 +2148,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>sm_dhr</t>
+          <t>sh_jssn</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>상상의 문 대학로점</t>
+          <t>셜록홈즈 잠실새내점 (T.A)</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -2163,12 +2163,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>sv_kd1</t>
+          <t>sm_dhr</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>솔버 1호점</t>
+          <t>상상의 문 대학로점</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -2178,12 +2178,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>sv_kd2</t>
+          <t>sv_kd1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>솔버 2호점</t>
+          <t>솔버 1호점</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -2193,12 +2193,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ui_sin</t>
+          <t>sv_kd2</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>나의신방</t>
+          <t>솔버 2호점</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2208,12 +2208,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>wy_hd</t>
+          <t>ui_sin</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>위욜</t>
+          <t>나의신방</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -2223,27 +2223,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>bp_101</t>
+          <t>wy_hd</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>비트포비아 던전101</t>
+          <t>위욜</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>bp_gd1</t>
+          <t>bp_101</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전</t>
+          <t>비트포비아 던전101</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2253,12 +2253,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>bp_hd1</t>
+          <t>bp_gd1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전</t>
+          <t>비트포비아 강남던전</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2268,12 +2268,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>bp_hd3</t>
+          <t>bp_hd1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>비트포비아 홍대던전3</t>
+          <t>비트포비아 홍대던전</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2283,12 +2283,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>bp_md</t>
+          <t>bp_hd3</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>비트포비아 명동점</t>
+          <t>비트포비아 홍대던전3</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2298,12 +2298,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>cde_ms</t>
+          <t>bp_md</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>코드이스케이프 마산점</t>
+          <t>비트포비아 명동점</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2313,12 +2313,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>de_gg</t>
+          <t>cde_ms</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>도어이스케이프 강남가든점</t>
+          <t>코드이스케이프 마산점</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2328,12 +2328,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>de_ls</t>
+          <t>de_gg</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>도어이스케이프 이수역점</t>
+          <t>도어이스케이프 강남가든점</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2343,12 +2343,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>dia_bs</t>
+          <t>de_ls</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>다이아에그 부산서면점</t>
+          <t>도어이스케이프 이수역점</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -2358,12 +2358,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>dm_dth</t>
+          <t>dia_bs</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>둠이스케이프 DTH점</t>
+          <t>다이아에그 부산서면점</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -2373,12 +2373,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>dm_gw1</t>
+          <t>dle_gn</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>둠이스케이프 1호점</t>
+          <t>돌로이스케이프</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2388,12 +2388,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>dm_gw2</t>
+          <t>dm_dth</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>둠이스케이프 2호점</t>
+          <t>둠이스케이프 DTH점</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2403,12 +2403,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>dps_ss</t>
+          <t>dm_gw1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>단편선 성수</t>
+          <t>둠이스케이프 1호점</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -2418,12 +2418,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>dre_kd</t>
+          <t>dm_gw2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>드림이스케이프 건대점</t>
+          <t>둠이스케이프 2호점</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -2433,12 +2433,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ect_bc</t>
+          <t>dps_ss</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>이스케이프시티 부천신중동점</t>
+          <t>단편선 성수</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2448,12 +2448,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ep_lg</t>
+          <t>dre_kd</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>에필로그</t>
+          <t>드림이스케이프 건대점</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2463,12 +2463,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>gaw_gn</t>
+          <t>ect_bc</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>겟어웨이 방탈출</t>
+          <t>이스케이프시티 부천신중동점</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2478,12 +2478,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>gom_sm</t>
+          <t>ep_lg</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>게임 오브 마인드 서면점</t>
+          <t>에필로그</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2493,12 +2493,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>gt_sw1</t>
+          <t>gaw_gn</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 1호점</t>
+          <t>겟어웨이 방탈출</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2508,12 +2508,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>he_gj</t>
+          <t>gom_sm</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>숨바꼭질 광주동구점</t>
+          <t>게임 오브 마인드 서면점</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2523,12 +2523,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>he_gj2</t>
+          <t>gt_sw1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>숨바꼭질 2호점</t>
+          <t>골든타임이스케이프 1호점</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2538,12 +2538,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>hp_ad</t>
+          <t>he_gj</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>해피앤딩</t>
+          <t>숨바꼭질 광주동구점</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2553,12 +2553,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>key_jj</t>
+          <t>hp_ad</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>키이스케이프 전주점</t>
+          <t>해피앤딩</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2568,12 +2568,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>last_esc</t>
+          <t>key_jj</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>라스트 이스케이프</t>
+          <t>키이스케이프 전주점</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2583,12 +2583,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>mk_dt</t>
+          <t>last_esc</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>마스터키프라임 동탄점</t>
+          <t>라스트 이스케이프</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2598,12 +2598,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>mp_is</t>
+          <t>mk_dt</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>머더파커 익산점</t>
+          <t>마스터키프라임 동탄점</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2613,12 +2613,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>mp_jj2</t>
+          <t>mp_is</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>머더파커 전주2호점 어드벤처</t>
+          <t>머더파커 익산점</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2628,12 +2628,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>mp_tg2</t>
+          <t>mp_jj2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>머더파커 대구2호점</t>
+          <t>머더파커 전주2호점 어드벤처</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2643,12 +2643,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>mpw_js</t>
+          <t>mp_tg2</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>머더파커 WOW 잠실점</t>
+          <t>머더파커 대구2호점</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2658,12 +2658,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>mre_hd2</t>
+          <t>mpw_js</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 홍대2호점</t>
+          <t>머더파커 WOW 잠실점</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2673,12 +2673,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>mt_sw</t>
+          <t>mre_hd2</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>메타이스케이프</t>
+          <t>미스터리 룸 이스케이프 홍대2호점</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2688,12 +2688,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>mz_kd</t>
+          <t>mt_sw</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>더메이즈 건대점</t>
+          <t>메타이스케이프</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -3708,12 +3708,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mz_kd</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>더메이즈 건대점</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3723,12 +3723,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3738,12 +3738,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3753,12 +3753,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3768,12 +3768,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3783,12 +3783,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3798,12 +3798,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3813,12 +3813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3828,12 +3828,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3843,12 +3843,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3858,12 +3858,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3873,12 +3873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3888,12 +3888,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3903,12 +3903,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ser_bp</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부평점</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3918,12 +3918,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ser_sm</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부산서면점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3933,12 +3933,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3948,12 +3948,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3963,12 +3963,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3978,12 +3978,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3993,12 +3993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4008,12 +4008,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4023,12 +4023,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4038,12 +4038,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4053,12 +4053,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4068,12 +4068,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4083,12 +4083,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4098,12 +4098,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4113,12 +4113,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4128,12 +4128,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4143,12 +4143,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4158,12 +4158,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4173,12 +4173,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4188,12 +4188,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4203,12 +4203,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4218,12 +4218,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4233,12 +4233,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>sh_yb</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인역북점 (T.A)</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4248,12 +4248,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sh_yb</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>셜록홈즈 용인역북점 (T.A)</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4263,12 +4263,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4308,12 +4308,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>wtw_esc</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>월투월방탈출 서울대입구점</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4323,12 +4323,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4338,27 +4338,27 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4368,12 +4368,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4383,12 +4383,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4398,12 +4398,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4413,12 +4413,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4428,12 +4428,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4443,12 +4443,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4458,12 +4458,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4473,12 +4473,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4488,12 +4488,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4503,12 +4503,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4518,12 +4518,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4533,12 +4533,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>fly_sw</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>THE FLIGHT</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4893,12 +4893,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4908,12 +4908,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4923,12 +4923,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4938,27 +4938,27 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C295" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4968,12 +4968,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4983,12 +4983,12 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4998,12 +4998,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>dia_inn</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리인</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5013,12 +5013,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>dia_inn</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>다이아에그 미스테리인</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5028,12 +5028,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5043,12 +5043,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5058,12 +5058,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5073,12 +5073,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5088,12 +5088,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5103,12 +5103,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5118,12 +5118,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5133,12 +5133,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5148,12 +5148,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5163,12 +5163,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5178,12 +5178,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5193,12 +5193,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5208,12 +5208,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5223,12 +5223,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5238,12 +5238,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5253,12 +5253,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5268,27 +5268,27 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C317" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5298,12 +5298,12 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5313,12 +5313,12 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -5328,12 +5328,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -5343,12 +5343,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ser_dsr</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 대구동성로점</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5358,12 +5358,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>ser_dsr</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>서울이스케이프룸 대구동성로점</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5373,12 +5373,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>sh_sw_2</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역2호점 (T.A)</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -5388,12 +5388,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>sh_sw_2</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>셜록홈즈 수원역2호점 (T.A)</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5403,27 +5403,27 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -5433,12 +5433,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -5448,27 +5448,27 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5478,27 +5478,27 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5508,27 +5508,27 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>otv_dj</t>
+          <t>zw_gp</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>오렌지티비 대전은행점</t>
+          <t>제로월드 김포본점</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>otv_dsr</t>
+          <t>otv_dj</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>오렌지티비 대구동성로점</t>
+          <t>오렌지티비 대전은행점</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5538,30 +5538,45 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>otv_dsr</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>오렌지티비 대구동성로점</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B337" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C336" t="n">
+      <c r="C337" t="n">
         <v>15</v>
       </c>
     </row>

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -993,27 +993,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>zw_kd</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>제로월드 다이브 건대점</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1023,12 +1023,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1038,12 +1038,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1053,12 +1053,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1068,12 +1068,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>dia_town</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>다이아에그 미스테리타운</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1083,12 +1083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dia_town</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리타운</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1098,12 +1098,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1113,12 +1113,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1128,12 +1128,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1143,12 +1143,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>ft_str3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>판타스트릭 TGC</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1158,12 +1158,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ft_str3</t>
+          <t>gk_ca</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>판타스트릭 TGC</t>
+          <t>황금열쇠 천안아케이드점</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1173,12 +1173,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>gk_ca</t>
+          <t>gk_fl</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>황금열쇠 천안아케이드점</t>
+          <t>황금열쇠 강남플라워로드점</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1188,12 +1188,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>gk_fl</t>
+          <t>gk_kd</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>황금열쇠 강남플라워로드점</t>
+          <t>황금열쇠 건대점</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1203,12 +1203,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gk_kd</t>
+          <t>gk_ts</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>황금열쇠 건대점</t>
+          <t>황금열쇠 강남타임스퀘어점</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1218,12 +1218,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>gk_ts</t>
+          <t>gt_sw2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>황금열쇠 강남타임스퀘어점</t>
+          <t>골든타임이스케이프 2호점</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1233,12 +1233,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gt_sw2</t>
+          <t>he_gj3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>골든타임이스케이프 2호점</t>
+          <t>숨바꼭질 3호점</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1248,12 +1248,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>he_gj3</t>
+          <t>hs_hd</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>숨바꼭질 3호점</t>
+          <t>히든스위치 홍대점</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1263,12 +1263,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>hs_hd</t>
+          <t>key_log1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>히든스위치 홍대점</t>
+          <t>키이스케이프 LOG_IN1</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1278,12 +1278,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>key_log1</t>
+          <t>key_to</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>키이스케이프 LOG_IN1</t>
+          <t>키이스케이프 강남 더오름</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1293,12 +1293,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>key_to</t>
+          <t>key_wl</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>키이스케이프 강남 더오름</t>
+          <t>키이스케이프 우주라이크</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1308,12 +1308,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>key_wl</t>
+          <t>live_c</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>키이스케이프 우주라이크</t>
+          <t>라이브시네마</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1323,12 +1323,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>live_c</t>
+          <t>ohp_gn</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>라이브시네마</t>
+          <t>오늘의 한 페이지</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1338,12 +1338,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ohp_gn</t>
+          <t>pn_hd</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>오늘의 한 페이지</t>
+          <t>포인트나인 홍대점</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1353,12 +1353,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>pn_hd</t>
+          <t>rex_ov</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>포인트나인 홍대점</t>
+          <t>룸익스케이프 OLIVE</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1368,12 +1368,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>rex_ov</t>
+          <t>rh_ct</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>룸익스케이프 OLIVE</t>
+          <t>러시아워 3호점 시네마틱</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1383,12 +1383,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>rh_ct</t>
+          <t>rle_hd1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>러시아워 3호점 시네마틱</t>
+          <t>룸엘이스케이프 홍대1호점</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1398,12 +1398,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>rle_hd1</t>
+          <t>sh_gj</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>룸엘이스케이프 홍대1호점</t>
+          <t>셜록홈즈 부산기장정관점</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1413,12 +1413,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sh_gj</t>
+          <t>sp_es</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산기장정관점</t>
+          <t>스피키지</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1428,12 +1428,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>sp_es</t>
+          <t>st_esc</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>스피키지</t>
+          <t>STUDIO ESC</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1443,12 +1443,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>st_esc</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>STUDIO ESC</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1458,12 +1458,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1473,12 +1473,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>zw_kd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>제로월드 다이브 건대점</t>
         </is>
       </c>
       <c r="C64" t="n">

--- a/store_compare.xlsx
+++ b/store_compare.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C337"/>
+  <dimension ref="A1:C341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -978,27 +978,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>swj_ig</t>
+          <t>bp_dl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>소우주 인계갤러리점</t>
+          <t>비트포비아 던전루나</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bp_dl</t>
+          <t>bp_gd2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>비트포비아 던전루나</t>
+          <t>비트포비아 강남던전2</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1008,12 +1008,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bp_gd2</t>
+          <t>ch27_bf</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비트포비아 강남던전2</t>
+          <t>채널 27 버터플라이점</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1023,12 +1023,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ch27_bf</t>
+          <t>de_hd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>채널 27 버터플라이점</t>
+          <t>도어이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1038,12 +1038,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>de_hd</t>
+          <t>de_sb</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>도어이스케이프 홍대점</t>
+          <t>도어이스케이프 신논현 블루점</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1053,12 +1053,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>de_sb</t>
+          <t>dia_town</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>도어이스케이프 신논현 블루점</t>
+          <t>다이아에그 미스테리타운</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1068,12 +1068,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dia_town</t>
+          <t>dps_gn</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리타운</t>
+          <t>단편선 강남</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1083,12 +1083,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>dps_gn</t>
+          <t>ecw_sw</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>단편선 강남</t>
+          <t>이스케이프월드</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1098,12 +1098,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ecw_sw</t>
+          <t>ed_gn</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>이스케이프월드</t>
+          <t>엑소더스 강남점</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1113,12 +1113,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ed_gn</t>
+          <t>es_rbh</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>엑소더스 강남점</t>
+          <t>방탈출 토끼굴</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1128,12 +1128,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>es_rbh</t>
+          <t>ex_es</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>방탈출 토끼굴</t>
+          <t>익스플로리아 이스케이프</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1443,12 +1443,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>the_ct</t>
+          <t>swj_ig</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>더챕터</t>
+          <t>소우주 인계갤러리점</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1458,12 +1458,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ts_hd</t>
+          <t>the_ct</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>테라스페이스 홍대점</t>
+          <t>더챕터</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1473,12 +1473,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>zw_kd</t>
+          <t>ts_hd</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>제로월드 다이브 건대점</t>
+          <t>테라스페이스 홍대점</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1488,12 +1488,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>zw_lt</t>
+          <t>zw_kd</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>제로월드X롯데월드</t>
+          <t>제로월드 다이브 건대점</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1503,16 +1503,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>33_dj</t>
+          <t>zw_lt</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PLAY33 대전점</t>
+          <t>제로월드X롯데월드</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -3258,12 +3258,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>bo_hd</t>
+          <t>33_dj</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>브레이크아웃 이스케이프 홍대점</t>
+          <t>PLAY33 대전점</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -3273,12 +3273,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>bs_td</t>
+          <t>bo_hd</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>버스티드</t>
+          <t>브레이크아웃 이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3288,12 +3288,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>cb_ic</t>
+          <t>bs_td</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>큐브이스케이프 인천구월점</t>
+          <t>버스티드</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3303,12 +3303,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>cc_hd</t>
+          <t>cb_ic</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>시크릿코드 홍대점</t>
+          <t>큐브이스케이프 인천구월점</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3318,12 +3318,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>crew_sc2</t>
+          <t>cc_hd</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>탐정크루 신촌2호점</t>
+          <t>시크릿코드 홍대점</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3333,12 +3333,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>dp_as1</t>
+          <t>crew_sc2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>꿈소풍 안산1호점</t>
+          <t>탐정크루 신촌2호점</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3348,12 +3348,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>dp_as2</t>
+          <t>dp_as1</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>꿈소풍 안산2호점</t>
+          <t>꿈소풍 안산1호점</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -3363,12 +3363,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ecp_hd1</t>
+          <t>dp_as2</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대1호점</t>
+          <t>꿈소풍 안산2호점</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3378,12 +3378,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ecp_hd2</t>
+          <t>ecp_hd1</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>이스케이퍼스 홍대2호점</t>
+          <t>이스케이퍼스 홍대1호점</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3393,12 +3393,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ecs_ss</t>
+          <t>ecp_hd2</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>이스케이프# 신사점</t>
+          <t>이스케이퍼스 홍대2호점</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3408,12 +3408,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ect_sswu</t>
+          <t>ecs_ss</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>이스케이프시티 성신여대점</t>
+          <t>이스케이프# 신사점</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3423,12 +3423,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>epsd_sh</t>
+          <t>ect_sswu</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>에피소드 방탈출 분당점</t>
+          <t>이스케이프시티 성신여대점</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3438,12 +3438,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>esc_hus</t>
+          <t>epsd_sh</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>방탈출 이스케이프 하우스</t>
+          <t>에피소드 방탈출 분당점</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3453,12 +3453,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>find_esc</t>
+          <t>esc_hus</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>더파인더 방탈출</t>
+          <t>방탈출 이스케이프 하우스</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3468,12 +3468,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>gk_dsr</t>
+          <t>find_esc</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로점</t>
+          <t>더파인더 방탈출</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3483,12 +3483,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>gt_dsr</t>
+          <t>gk_dsr</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>시간의 문 대구동성로점</t>
+          <t>황금열쇠 대구동성로점</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3498,12 +3498,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>key_bs</t>
+          <t>gt_dsr</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>키이스케이프 부산점</t>
+          <t>시간의 문 대구동성로점</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3513,12 +3513,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>mi_ro</t>
+          <t>key_bs</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>방탈출미로</t>
+          <t>키이스케이프 부산점</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3528,12 +3528,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>mk_ay</t>
+          <t>mi_ro</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>마스터키 안양점</t>
+          <t>방탈출미로</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -3543,12 +3543,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>mk_cj</t>
+          <t>mk_ay</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>마스터키프라임 청주점</t>
+          <t>마스터키 안양점</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -3558,12 +3558,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>mk_deh</t>
+          <t>mk_cj</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>마스터키 은행직영점</t>
+          <t>마스터키프라임 청주점</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -3573,12 +3573,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>mk_dgd</t>
+          <t>mk_deh</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>마스터키 궁동직영점</t>
+          <t>마스터키 은행직영점</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -3588,12 +3588,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>mp_bs</t>
+          <t>mk_dgd</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>머더파커 부산점</t>
+          <t>마스터키 궁동직영점</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3603,12 +3603,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>mp_gj</t>
+          <t>mp_bs</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>머더파커 광주점</t>
+          <t>머더파커 부산점</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3618,12 +3618,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>mp_hd1</t>
+          <t>mp_gj</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>머더파커 홍대1호점</t>
+          <t>머더파커 광주점</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3633,12 +3633,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>mp_jj3</t>
+          <t>mp_hd1</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>머더파커 전주3호점 E.T</t>
+          <t>머더파커 홍대1호점</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3648,12 +3648,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>mp_tg1</t>
+          <t>mp_jj3</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>머더파커 대구1호점</t>
+          <t>머더파커 전주3호점 E.T</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3663,12 +3663,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>mp_ys</t>
+          <t>mp_tg1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>머더파커 양산점</t>
+          <t>머더파커 대구1호점</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3678,12 +3678,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>mre_gn</t>
+          <t>mp_ys</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>미스터리 룸 이스케이프 강남점</t>
+          <t>머더파커 양산점</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3693,12 +3693,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>mrj_kn</t>
+          <t>mre_gn</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>명란젓코난</t>
+          <t>미스터리 룸 이스케이프 강남점</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3708,12 +3708,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>mz_kd</t>
+          <t>mrj_kn</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>더메이즈 건대점</t>
+          <t>명란젓코난</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3723,12 +3723,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ne_sl</t>
+          <t>mz_kd</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>넥스트에디션 신림점</t>
+          <t>더메이즈 건대점</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3738,12 +3738,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ptw_bp</t>
+          <t>ne_sl</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>플레이더월드 부평점</t>
+          <t>넥스트에디션 신림점</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3753,12 +3753,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ptw_kd</t>
+          <t>ptw_bp</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>플레이더월드 건대점</t>
+          <t>플레이더월드 부평점</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3768,12 +3768,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ra_dhr</t>
+          <t>ptw_kd</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>룸즈에이 대학로점</t>
+          <t>플레이더월드 건대점</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -3783,12 +3783,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ra_dsr</t>
+          <t>ra_dhr</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로점</t>
+          <t>룸즈에이 대학로점</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -3798,12 +3798,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ra_dsra</t>
+          <t>ra_dsr</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>룸즈에이 동성로아카데미점</t>
+          <t>룸즈에이 대구동성로점</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -3813,12 +3813,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ra_gn</t>
+          <t>ra_dsra</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>룸즈에이 강남점</t>
+          <t>룸즈에이 동성로아카데미점</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3828,12 +3828,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ra_ui</t>
+          <t>ra_gn</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>룸즈에이 의정부점</t>
+          <t>룸즈에이 강남점</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3843,12 +3843,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ra_wd</t>
+          <t>ra_ui</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>룸즈에이 일산 웨스턴돔점</t>
+          <t>룸즈에이 의정부점</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -3858,12 +3858,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>rec_hd</t>
+          <t>ra_wd</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>리얼 이스케이프 첼린지</t>
+          <t>룸즈에이 일산 웨스턴돔점</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3873,12 +3873,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>rex_wh</t>
+          <t>rec_hd</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>룸익스케이프 WHITE</t>
+          <t>리얼 이스케이프 첼린지</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -3888,12 +3888,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>rs_hr</t>
+          <t>rex_wh</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>러시아워</t>
+          <t>룸익스케이프 WHITE</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3903,12 +3903,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>se_sw</t>
+          <t>rs_hr</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>싸인이스케이프 성대역점</t>
+          <t>러시아워</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -3918,12 +3918,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ser_bp</t>
+          <t>se_sw</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부평점</t>
+          <t>싸인이스케이프 성대역점</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3933,12 +3933,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ser_sm</t>
+          <t>ser_bp</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 부산서면점</t>
+          <t>서울이스케이프룸 부평점</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3948,12 +3948,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>sfr_hd</t>
+          <t>ser_sm</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>비밀의 숲 홍대점</t>
+          <t>서울이스케이프룸 부산서면점</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -3963,12 +3963,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>sg_dhr</t>
+          <t>sfr_hd</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>비밀의 화원 대학로점</t>
+          <t>비밀의 숲 홍대점</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3978,12 +3978,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>sg_hh</t>
+          <t>sg_dhr</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>비밀의 화원 시네마틱 혜화점</t>
+          <t>비밀의 화원 대학로점</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3993,12 +3993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>sgn_dt</t>
+          <t>sg_hh</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>시그널헌터 동탄점</t>
+          <t>비밀의 화원 시네마틱 혜화점</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -4008,12 +4008,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>sgn_sw</t>
+          <t>sgn_dt</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>시그널헌터 광교중앙점</t>
+          <t>시그널헌터 동탄점</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4023,12 +4023,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>sh_art</t>
+          <t>sgn_sw</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
+          <t>시그널헌터 광교중앙점</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4038,12 +4038,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>sh_as</t>
+          <t>sh_art</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>셜록홈즈 아산점</t>
+          <t>셜록홈즈 부산 아트몰링 (T.A)</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4053,12 +4053,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>sh_ay</t>
+          <t>sh_as</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴안양점</t>
+          <t>셜록홈즈 아산점</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4068,12 +4068,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>sh_bp2</t>
+          <t>sh_ay</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평2호점</t>
+          <t>셜록홈즈 뉴안양점</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4083,12 +4083,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>sh_ca1</t>
+          <t>sh_bp2</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>셜록홈즈 천안1호점</t>
+          <t>셜록홈즈 부평2호점</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4098,12 +4098,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>sh_cj</t>
+          <t>sh_ca1</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>셜록홈즈 청주점</t>
+          <t>셜록홈즈 천안1호점</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4113,12 +4113,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>sh_dhr</t>
+          <t>sh_cj</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>셜록홈즈 대학로점</t>
+          <t>셜록홈즈 청주점</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4128,12 +4128,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>sh_gp</t>
+          <t>sh_dhr</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>셜록홈즈 김포구래점 (T.A)</t>
+          <t>셜록홈즈 대학로점</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4143,12 +4143,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>sh_gr</t>
+          <t>sh_djds</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>셜록홈즈 구리점</t>
+          <t>셜록홈즈 대전둔산점 (T.A)</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4158,12 +4158,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>sh_gs</t>
+          <t>sh_gp</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>셜록홈즈 군산수송점 (T.A)</t>
+          <t>셜록홈즈 김포구래점 (T.A)</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -4173,12 +4173,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>sh_jg</t>
+          <t>sh_gr</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>셜록홈즈 종각점</t>
+          <t>셜록홈즈 구리점</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4188,12 +4188,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>sh_pt</t>
+          <t>sh_gs</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>셜록홈즈 평택점</t>
+          <t>셜록홈즈 군산수송점 (T.A)</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4203,12 +4203,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>sh_sj</t>
+          <t>sh_jg</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>셜록홈즈 수지구청점 (T.A)</t>
+          <t>셜록홈즈 종각점</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4218,12 +4218,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>sh_ujb</t>
+          <t>sh_pt</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>셜록홈즈 의정부점</t>
+          <t>셜록홈즈 평택점</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4233,12 +4233,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>sh_wj</t>
+          <t>sh_sj</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>셜록홈즈 원주점 (T.A)</t>
+          <t>셜록홈즈 수지구청점 (T.A)</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4248,12 +4248,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>sh_yb</t>
+          <t>sh_ujb</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인역북점 (T.A)</t>
+          <t>셜록홈즈 의정부점</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4263,12 +4263,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>sh_yt</t>
+          <t>sh_wj</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>셜록홈즈 분당야탑점</t>
+          <t>셜록홈즈 원주점 (T.A)</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4278,12 +4278,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>tcd_sgp</t>
+          <t>sh_yb</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>더 코드 제주서귀포점</t>
+          <t>셜록홈즈 용인역북점 (T.A)</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4293,12 +4293,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>trap_sy</t>
+          <t>sh_yt</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>더트랩 수유점</t>
+          <t>셜록홈즈 분당야탑점</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4308,12 +4308,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>xcp_sw</t>
+          <t>tcd_sgp</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>엑스케이프 수원점</t>
+          <t>더 코드 제주서귀포점</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4323,12 +4323,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>zw_hd</t>
+          <t>trap_sy</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>제로월드 홍대점</t>
+          <t>더트랩 수유점</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4338,42 +4338,42 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>bp_sdr</t>
+          <t>xcp_sw</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>비트포비아 서면던전 레드</t>
+          <t>엑스케이프 수원점</t>
         </is>
       </c>
       <c r="C255" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>cb_dj</t>
+          <t>zw_hd</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>큐브이스케이프 대전둔산점</t>
+          <t>제로월드 홍대점</t>
         </is>
       </c>
       <c r="C256" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>cb_js</t>
+          <t>bp_sdr</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>큐브이스케이프 잠실점</t>
+          <t>비트포비아 서면던전 레드</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4383,12 +4383,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>d_doo</t>
+          <t>cb_dj</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>방탈출, 둡두</t>
+          <t>큐브이스케이프 대전둔산점</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -4398,12 +4398,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>dd_dhr</t>
+          <t>cb_js</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>덤앤더머 대학로점</t>
+          <t>큐브이스케이프 잠실점</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4413,12 +4413,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>de_as</t>
+          <t>d_doo</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>도어이스케이프 안산점</t>
+          <t>방탈출, 둡두</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -4428,12 +4428,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>de_dj</t>
+          <t>dd_dhr</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>도어이스케이프 대전유성 NC백화점</t>
+          <t>덤앤더머 대학로점</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -4443,12 +4443,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>dp_bc</t>
+          <t>de_as</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>꿈소풍 부천점</t>
+          <t>도어이스케이프 안산점</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4458,12 +4458,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ecp_dj</t>
+          <t>de_dj</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>이스케이퍼스 AFSC</t>
+          <t>도어이스케이프 대전유성 NC백화점</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -4473,12 +4473,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ecp_dsr</t>
+          <t>dp_bc</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>이스케이퍼스 대구동성로점</t>
+          <t>꿈소풍 부천점</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -4488,12 +4488,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ect_ydp</t>
+          <t>ecp_dj</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>이스케이프시티 영등포본점</t>
+          <t>이스케이퍼스 AFSC</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -4503,12 +4503,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ee_av</t>
+          <t>ecp_dsr</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>지구별방탈출 어드벤처점</t>
+          <t>이스케이퍼스 대구동성로점</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4518,12 +4518,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>esc_bro</t>
+          <t>ect_ydp</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>탈출 브라더스</t>
+          <t>이스케이프시티 영등포본점</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4533,12 +4533,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>fly_sw</t>
+          <t>ee_av</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>THE FLIGHT</t>
+          <t>지구별방탈출 어드벤처점</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4548,12 +4548,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>key_mm</t>
+          <t>esc_bro</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>키이스케이프 무비무드</t>
+          <t>탈출 브라더스</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4563,12 +4563,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>mk_hj</t>
+          <t>fly_sw</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>마스터키프라임 화정점</t>
+          <t>THE FLIGHT</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4578,12 +4578,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>mp_kd1</t>
+          <t>key_mm</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>머더파커 건대1호점</t>
+          <t>키이스케이프 무비무드</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4593,12 +4593,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ne_bs</t>
+          <t>mk_hj</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>넥스트에디션 분당서현점</t>
+          <t>마스터키프라임 화정점</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4608,12 +4608,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ne_kd1</t>
+          <t>mp_kd1</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대1호점</t>
+          <t>머더파커 건대1호점</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4623,12 +4623,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ppl_cd</t>
+          <t>ne_bs</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안두정점</t>
+          <t>넥스트에디션 분당서현점</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4638,12 +4638,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ppl_cp</t>
+          <t>ne_kd1</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>플레이포인트랩 천안프리미엄점</t>
+          <t>넥스트에디션 건대1호점</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4653,12 +4653,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ppl_gn</t>
+          <t>ppl_cd</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>플레이포인트랩 강남점</t>
+          <t>플레이포인트랩 천안두정점</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4668,12 +4668,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ppl_hbs</t>
+          <t>ppl_cp</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>플레이포인트랩 해운대 블루오션스테이션</t>
+          <t>플레이포인트랩 천안프리미엄점</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -4683,12 +4683,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ppl_js</t>
+          <t>ppl_gn</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>플레이포인트랩 잠실점</t>
+          <t>플레이포인트랩 강남점</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4698,12 +4698,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ptw_gn</t>
+          <t>ppl_hbs</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>플레이더월드 강남점</t>
+          <t>플레이포인트랩 해운대 블루오션스테이션</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4713,12 +4713,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ptw_pt</t>
+          <t>ppl_js</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>플레이더월드 평택점</t>
+          <t>플레이포인트랩 잠실점</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4728,12 +4728,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ra_ds</t>
+          <t>ptw_gn</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>룸즈에이 대전둔산점</t>
+          <t>플레이더월드 강남점</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4743,12 +4743,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ra_dsr2</t>
+          <t>ptw_pt</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>룸즈에이 대구동성로2호점</t>
+          <t>플레이더월드 평택점</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -4758,12 +4758,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ra_np</t>
+          <t>ra_ds</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>룸즈에이 부산남포점</t>
+          <t>룸즈에이 대전둔산점</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4773,12 +4773,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ra_psm</t>
+          <t>ra_dsr2</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>룸즈에이 부산서면점</t>
+          <t>룸즈에이 대구동성로2호점</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4788,12 +4788,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sg_kd</t>
+          <t>ra_np</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>비밀의 화원 건대점</t>
+          <t>룸즈에이 부산남포점</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -4803,12 +4803,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sh_bp</t>
+          <t>ra_psm</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>셜록홈즈 부평점</t>
+          <t>룸즈에이 부산서면점</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4818,12 +4818,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>sh_dt</t>
+          <t>sg_kd</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>셜록홈즈 동탄점</t>
+          <t>비밀의 화원 건대점</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4833,12 +4833,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>sh_gw</t>
+          <t>sh_ans</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>셜록홈즈 구월인천점</t>
+          <t>셜록홈즈 안산점 (T.A)</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4848,12 +4848,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>sh_nbc</t>
+          <t>sh_bp</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>셜록홈즈 뉴부천점</t>
+          <t>셜록홈즈 부평점</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4863,12 +4863,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>sh_nw</t>
+          <t>sh_dt</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>셜록홈즈 노원점</t>
+          <t>셜록홈즈 동탄점</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4878,12 +4878,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>sm_bs</t>
+          <t>sh_gw</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>상상의 문 분당서현점</t>
+          <t>셜록홈즈 구월인천점</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4893,12 +4893,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>sm_gj</t>
+          <t>sh_nbc</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>상상의 문 광주점</t>
+          <t>셜록홈즈 뉴부천점</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4908,12 +4908,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>sm_sw1</t>
+          <t>sh_nw</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>상상의 문 수원점</t>
+          <t>셜록홈즈 노원점</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -4923,12 +4923,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>sm_sw2</t>
+          <t>sm_bs</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>상상의 문 수원2호점</t>
+          <t>상상의 문 분당서현점</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -4938,12 +4938,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>xcp_hd</t>
+          <t>sm_gj</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>엑스케이프 홍대점</t>
+          <t>상상의 문 광주점</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -4953,57 +4953,57 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>cb_ch</t>
+          <t>sm_sw1</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>큐브이스케이프 천호점</t>
+          <t>상상의 문 수원점</t>
         </is>
       </c>
       <c r="C296" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>cb_sy</t>
+          <t>sm_sw2</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>큐브이스케이프 수유점</t>
+          <t>상상의 문 수원2호점</t>
         </is>
       </c>
       <c r="C297" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>dd_hd</t>
+          <t>xcp_hd</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>덤앤더머 홍대점</t>
+          <t>엑스케이프 홍대점</t>
         </is>
       </c>
       <c r="C298" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>dh_gn</t>
+          <t>cb_ch</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>개꿀이스케이프</t>
+          <t>큐브이스케이프 천호점</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5013,12 +5013,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>dia_inn</t>
+          <t>cb_sy</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>다이아에그 미스테리인</t>
+          <t>큐브이스케이프 수유점</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5028,12 +5028,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ee_tg</t>
+          <t>dd_hd</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>지구별방탈출 대구점</t>
+          <t>덤앤더머 홍대점</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -5043,12 +5043,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>lk_wd</t>
+          <t>dh_gn</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>링크월드</t>
+          <t>개꿀이스케이프</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -5058,12 +5058,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ne_kd2</t>
+          <t>dia_inn</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>넥스트에디션 건대2호점</t>
+          <t>다이아에그 미스테리인</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5073,12 +5073,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ptw_dj</t>
+          <t>ee_tg</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>플레이더월드 대전은행점</t>
+          <t>지구별방탈출 대구점</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5088,12 +5088,12 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ra_gsw</t>
+          <t>lbrt_es</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>룸즈에이 광주수완점</t>
+          <t>라비린스 이스케이프</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5103,12 +5103,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>sg_dsr</t>
+          <t>lk_wd</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>비밀의 화원 동성로점</t>
+          <t>링크월드</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5118,12 +5118,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>sg_gj</t>
+          <t>ne_kd2</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>비밀의 화원 광주점</t>
+          <t>넥스트에디션 건대2호점</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5133,12 +5133,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>sg_sm</t>
+          <t>ptw_dj</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>비밀의 화원 서면점</t>
+          <t>플레이더월드 대전은행점</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5148,12 +5148,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>sh_bg</t>
+          <t>ra_gsw</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>셜록홈즈 안양범계점 (T.A)</t>
+          <t>룸즈에이 광주수완점</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5163,12 +5163,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>sh_ig</t>
+          <t>sg_dsr</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원인계점 (T.A)</t>
+          <t>비밀의 화원 동성로점</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5178,12 +5178,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>sh_js</t>
+          <t>sg_gj</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>셜록홈즈 잠실점</t>
+          <t>비밀의 화원 광주점</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -5193,12 +5193,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>sh_sd</t>
+          <t>sg_sm</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>셜록홈즈 송도트리플점 (T.A)</t>
+          <t>비밀의 화원 서면점</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5208,12 +5208,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>sh_sw</t>
+          <t>sh_bg</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역점 (T.A)</t>
+          <t>셜록홈즈 안양범계점 (T.A)</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5223,12 +5223,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>sh_ys</t>
+          <t>sh_ig</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>셜록홈즈 여수점</t>
+          <t>셜록홈즈 수원인계점 (T.A)</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5238,12 +5238,12 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>swj_sw</t>
+          <t>sh_js</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>소우주</t>
+          <t>셜록홈즈 잠실점</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5253,12 +5253,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>tcd_jj</t>
+          <t>sh_sd</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>더 코드 진주점</t>
+          <t>셜록홈즈 송도트리플점 (T.A)</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5268,12 +5268,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>zw_sh</t>
+          <t>sh_sw</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>제로월드 서현점</t>
+          <t>셜록홈즈 수원역점 (T.A)</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5283,72 +5283,72 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>cb_hd</t>
+          <t>sh_ys</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>큐브이스케이프 홍대점</t>
+          <t>셜록홈즈 여수점</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>cb_jj</t>
+          <t>swj_sw</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>큐브이스케이프 전주점</t>
+          <t>소우주</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ee_lc</t>
+          <t>tcd_jj</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>지구별방탈출 라스트시티점</t>
+          <t>더 코드 진주점</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>er8_gn</t>
+          <t>zw_sh</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>이룸에이트</t>
+          <t>제로월드 서현점</t>
         </is>
       </c>
       <c r="C321" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>gk_tk</t>
+          <t>cb_hd</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>황금열쇠 대구동성로2호점</t>
+          <t>큐브이스케이프 홍대점</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -5358,12 +5358,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ser_dsr</t>
+          <t>cb_jj</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>서울이스케이프룸 대구동성로점</t>
+          <t>큐브이스케이프 전주점</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5373,12 +5373,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>sh_db</t>
+          <t>ee_lc</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>셜록홈즈 용인동백점 (T.A)</t>
+          <t>지구별방탈출 라스트시티점</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -5388,12 +5388,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>sh_sw_2</t>
+          <t>er8_gn</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>셜록홈즈 수원역2호점 (T.A)</t>
+          <t>이룸에이트</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5403,12 +5403,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>tcd_jgj</t>
+          <t>gk_tk</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>더 코드 광주</t>
+          <t>황금열쇠 대구동성로2호점</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5418,165 +5418,225 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>gt_gj</t>
+          <t>ser_dsr</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>시간의 문 광주점</t>
+          <t>서울이스케이프룸 대구동성로점</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ra_sm</t>
+          <t>sh_db</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>룸즈에이 광주상무점</t>
+          <t>셜록홈즈 용인동백점 (T.A)</t>
         </is>
       </c>
       <c r="C328" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>zw_gn</t>
+          <t>sh_sw_2</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>제로월드 강남점</t>
+          <t>셜록홈즈 수원역2호점 (T.A)</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ecs_kd</t>
+          <t>tcd_jgj</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>이스케이프# 건대점</t>
+          <t>더 코드 광주</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>mz_nw</t>
+          <t>gt_gj</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>더메이즈 노원점</t>
+          <t>시간의 문 광주점</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>dd_sm</t>
+          <t>ra_sm</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>덤앤더머 서면점</t>
+          <t>룸즈에이 광주상무점</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>zw_gp</t>
+          <t>zw_gn</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>제로월드 김포본점</t>
+          <t>제로월드 강남점</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>otv_dj</t>
+          <t>ecs_kd</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>오렌지티비 대전은행점</t>
+          <t>이스케이프# 건대점</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>otv_dsr</t>
+          <t>mz_nw</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>오렌지티비 대구동성로점</t>
+          <t>더메이즈 노원점</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ck_gn</t>
+          <t>dd_sm</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>코드케이 강남점</t>
+          <t>덤앤더머 서면점</t>
         </is>
       </c>
       <c r="C336" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
+          <t>zw_gp</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>제로월드 김포본점</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>otv_dj</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>오렌지티비 대전은행점</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>otv_dsr</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>오렌지티비 대구동성로점</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>ck_gn</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>코드케이 강남점</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
           <t>tte_hd</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B341" t="inlineStr">
         <is>
           <t>티켓투이스케이프</t>
         </is>
       </c>
-      <c r="C337" t="n">
+      <c r="C341" t="n">
         <v>15</v>
       </c>
     </row>
